--- a/artfynd/A 39682-2025 artfynd.xlsx
+++ b/artfynd/A 39682-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY32"/>
+  <dimension ref="A1:AY33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1236,48 +1236,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128838010</v>
+        <v>128838005</v>
       </c>
       <c r="B7" t="n">
-        <v>79116</v>
+        <v>43979</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>101735</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hästmyr, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>496332</v>
+        <v>496344</v>
       </c>
       <c r="R7" t="n">
-        <v>6779876</v>
+        <v>6779645</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1309,7 +1306,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1319,12 +1316,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:17</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1352,45 +1344,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128838005</v>
+        <v>128838010</v>
       </c>
       <c r="B8" t="n">
-        <v>43979</v>
+        <v>79116</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>101735</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hästmyr, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>496344</v>
+        <v>496332</v>
       </c>
       <c r="R8" t="n">
-        <v>6779645</v>
+        <v>6779876</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1422,7 +1417,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1427,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1567,32 +1567,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128838045</v>
+        <v>128838011</v>
       </c>
       <c r="B10" t="n">
-        <v>43979</v>
+        <v>79116</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>101735</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1602,10 +1602,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>496345</v>
+        <v>496295</v>
       </c>
       <c r="R10" t="n">
-        <v>6780049</v>
+        <v>6779954</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1656,7 +1656,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1675,32 +1674,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128838011</v>
+        <v>128838045</v>
       </c>
       <c r="B11" t="n">
-        <v>79116</v>
+        <v>43979</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>101735</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1710,10 +1709,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>496295</v>
+        <v>496345</v>
       </c>
       <c r="R11" t="n">
-        <v>6779954</v>
+        <v>6780049</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1745,7 +1744,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1755,7 +1754,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1764,6 +1763,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1782,7 +1782,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128838048</v>
+        <v>128838046</v>
       </c>
       <c r="B12" t="n">
         <v>79116</v>
@@ -1811,16 +1811,19 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hästmyr, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>496271</v>
+        <v>496348</v>
       </c>
       <c r="R12" t="n">
-        <v>6780378</v>
+        <v>6780084</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1852,7 +1855,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1862,7 +1865,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1871,6 +1879,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1889,7 +1898,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128838046</v>
+        <v>128838048</v>
       </c>
       <c r="B13" t="n">
         <v>79116</v>
@@ -1918,19 +1927,16 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hästmyr, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>496348</v>
+        <v>496271</v>
       </c>
       <c r="R13" t="n">
-        <v>6780084</v>
+        <v>6780378</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1962,7 +1968,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1972,12 +1978,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:51</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1986,7 +1987,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2005,7 +2005,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128838050</v>
+        <v>128838049</v>
       </c>
       <c r="B14" t="n">
         <v>79116</v>
@@ -2040,10 +2040,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>496259</v>
+        <v>496350</v>
       </c>
       <c r="R14" t="n">
-        <v>6780405</v>
+        <v>6780093</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2085,7 +2085,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2112,7 +2112,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128838049</v>
+        <v>128838009</v>
       </c>
       <c r="B15" t="n">
         <v>79116</v>
@@ -2141,16 +2141,19 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Hästmyr, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>496350</v>
+        <v>496340</v>
       </c>
       <c r="R15" t="n">
-        <v>6780093</v>
+        <v>6779846</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2182,7 +2185,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2192,7 +2195,12 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>15:23</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2201,6 +2209,7 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
+      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2219,7 +2228,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128838009</v>
+        <v>128838050</v>
       </c>
       <c r="B16" t="n">
         <v>79116</v>
@@ -2248,19 +2257,16 @@
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Hästmyr, Dlr</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>496340</v>
+        <v>496259</v>
       </c>
       <c r="R16" t="n">
-        <v>6779846</v>
+        <v>6780405</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2292,7 +2298,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2302,12 +2308,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:23</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2316,7 +2317,6 @@
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
@@ -2442,48 +2442,48 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128838052</v>
+        <v>128842520</v>
       </c>
       <c r="B18" t="n">
-        <v>92784</v>
+        <v>57716</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Hästmyr, Dlr</t>
+          <t>Hästmyr, Hästmyr, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>496237</v>
+        <v>496283</v>
       </c>
       <c r="R18" t="n">
-        <v>6780285</v>
+        <v>6779932</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2522,7 +2522,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Bohål I Björk</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2531,67 +2536,63 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Jakob Bowers</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Jakob Bowers</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128838007</v>
+        <v>128838052</v>
       </c>
       <c r="B19" t="n">
-        <v>79116</v>
+        <v>92784</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
           <t>Hästmyr, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>496367</v>
+        <v>496237</v>
       </c>
       <c r="R19" t="n">
-        <v>6779675</v>
+        <v>6780285</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2623,7 +2624,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2633,12 +2634,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:35</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2666,7 +2662,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128838020</v>
+        <v>128838007</v>
       </c>
       <c r="B20" t="n">
         <v>79116</v>
@@ -2695,16 +2691,19 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hästmyr, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>496336</v>
+        <v>496367</v>
       </c>
       <c r="R20" t="n">
-        <v>6779865</v>
+        <v>6779675</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2736,7 +2735,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2746,7 +2745,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2755,6 +2759,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2773,32 +2778,32 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128838021</v>
+        <v>128838020</v>
       </c>
       <c r="B21" t="n">
-        <v>92784</v>
+        <v>79116</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2808,10 +2813,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>496349</v>
+        <v>496336</v>
       </c>
       <c r="R21" t="n">
-        <v>6779557</v>
+        <v>6779865</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2843,7 +2848,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2853,7 +2858,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -3095,32 +3100,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128838014</v>
+        <v>128838021</v>
       </c>
       <c r="B24" t="n">
-        <v>79116</v>
+        <v>92784</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3130,10 +3135,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>496306</v>
+        <v>496349</v>
       </c>
       <c r="R24" t="n">
-        <v>6779793</v>
+        <v>6779557</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3165,7 +3170,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3175,7 +3180,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3202,10 +3207,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128837995</v>
+        <v>128838014</v>
       </c>
       <c r="B25" t="n">
-        <v>90526</v>
+        <v>79116</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3213,21 +3218,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1962</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3237,10 +3242,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>496293</v>
+        <v>496306</v>
       </c>
       <c r="R25" t="n">
-        <v>6779895</v>
+        <v>6779793</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3272,7 +3277,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3282,7 +3287,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3291,7 +3296,6 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
-      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3310,10 +3314,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128837997</v>
+        <v>128837995</v>
       </c>
       <c r="B26" t="n">
-        <v>79735</v>
+        <v>90526</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3321,21 +3325,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6453</v>
+        <v>1962</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3345,10 +3349,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>496278</v>
+        <v>496293</v>
       </c>
       <c r="R26" t="n">
-        <v>6779883</v>
+        <v>6779895</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3380,7 +3384,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3390,7 +3394,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3418,32 +3422,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128838042</v>
+        <v>128837997</v>
       </c>
       <c r="B27" t="n">
-        <v>8450</v>
+        <v>79735</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>106545</v>
+        <v>6453</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3453,10 +3457,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>496270</v>
+        <v>496278</v>
       </c>
       <c r="R27" t="n">
-        <v>6780214</v>
+        <v>6779883</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3488,7 +3492,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3498,7 +3502,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3507,6 +3511,7 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
+      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3645,32 +3650,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128838019</v>
+        <v>128838042</v>
       </c>
       <c r="B29" t="n">
-        <v>79116</v>
+        <v>8450</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3680,10 +3685,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>496340</v>
+        <v>496270</v>
       </c>
       <c r="R29" t="n">
-        <v>6779850</v>
+        <v>6780214</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3715,7 +3720,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3725,7 +3730,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3752,7 +3757,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128838015</v>
+        <v>128838019</v>
       </c>
       <c r="B30" t="n">
         <v>79116</v>
@@ -3787,10 +3792,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>496343</v>
+        <v>496340</v>
       </c>
       <c r="R30" t="n">
-        <v>6779566</v>
+        <v>6779850</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3822,7 +3827,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3832,7 +3837,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3859,7 +3864,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128838013</v>
+        <v>128838015</v>
       </c>
       <c r="B31" t="n">
         <v>79116</v>
@@ -3894,10 +3899,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>496280</v>
+        <v>496343</v>
       </c>
       <c r="R31" t="n">
-        <v>6779962</v>
+        <v>6779566</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3929,7 +3934,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3939,7 +3944,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4071,6 +4076,113 @@
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>128838013</v>
+      </c>
+      <c r="B33" t="n">
+        <v>79116</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Hästmyr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>496280</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6779962</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>16:34</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>16:34</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Jakob Bowers</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Jakob Bowers</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 39682-2025 artfynd.xlsx
+++ b/artfynd/A 39682-2025 artfynd.xlsx
@@ -675,53 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128838036</v>
+        <v>128838055</v>
       </c>
       <c r="B2" t="n">
-        <v>57716</v>
+        <v>92789</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hästmyr, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>496264</v>
+        <v>496351</v>
       </c>
       <c r="R2" t="n">
-        <v>6780257</v>
+        <v>6780081</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,12 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:43</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack högt på tall</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,45 +782,53 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128838055</v>
+        <v>128838036</v>
       </c>
       <c r="B3" t="n">
-        <v>92784</v>
+        <v>57716</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hästmyr, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>496351</v>
+        <v>496264</v>
       </c>
       <c r="R3" t="n">
-        <v>6780081</v>
+        <v>6780257</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -875,7 +870,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack högt på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,7 +905,7 @@
         <v>128838023</v>
       </c>
       <c r="B4" t="n">
-        <v>92784</v>
+        <v>92789</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
         <v>128838012</v>
       </c>
       <c r="B5" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1116,10 +1116,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128838001</v>
+        <v>128838010</v>
       </c>
       <c r="B6" t="n">
-        <v>57716</v>
+        <v>79120</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1127,31 +1127,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1159,10 +1154,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>496347</v>
+        <v>496332</v>
       </c>
       <c r="R6" t="n">
-        <v>6779846</v>
+        <v>6779876</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,7 +1189,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1204,12 +1199,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack högt upp på tall</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1218,6 +1213,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1236,45 +1232,53 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128838005</v>
+        <v>128838001</v>
       </c>
       <c r="B7" t="n">
-        <v>43979</v>
+        <v>57716</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>101735</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hästmyr, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>496344</v>
+        <v>496347</v>
       </c>
       <c r="R7" t="n">
-        <v>6779645</v>
+        <v>6779846</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1306,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1316,7 +1320,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack högt upp på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1325,7 +1334,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1344,48 +1352,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128838010</v>
+        <v>128838005</v>
       </c>
       <c r="B8" t="n">
-        <v>79116</v>
+        <v>43979</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>101735</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hästmyr, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>496332</v>
+        <v>496344</v>
       </c>
       <c r="R8" t="n">
-        <v>6779876</v>
+        <v>6779645</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1427,12 +1432,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:17</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1463,7 +1463,7 @@
         <v>128838047</v>
       </c>
       <c r="B9" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         <v>128838011</v>
       </c>
       <c r="B10" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         <v>128838046</v>
       </c>
       <c r="B12" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         <v>128838048</v>
       </c>
       <c r="B13" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2008,7 +2008,7 @@
         <v>128838049</v>
       </c>
       <c r="B14" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2115,7 +2115,7 @@
         <v>128838009</v>
       </c>
       <c r="B15" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
         <v>128838050</v>
       </c>
       <c r="B16" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>128838017</v>
       </c>
       <c r="B17" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2442,48 +2442,48 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128842520</v>
+        <v>128838052</v>
       </c>
       <c r="B18" t="n">
-        <v>57716</v>
+        <v>92789</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Hästmyr, Hästmyr, Dlr</t>
+          <t>Hästmyr, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>496283</v>
+        <v>496237</v>
       </c>
       <c r="R18" t="n">
-        <v>6779932</v>
+        <v>6780285</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2522,12 +2522,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Bohål I Björk</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2536,66 +2531,67 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Jakob Bowers</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Jakob Bowers</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128838052</v>
+        <v>128842520</v>
       </c>
       <c r="B19" t="n">
-        <v>92784</v>
+        <v>57716</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Hästmyr, Dlr</t>
+          <t>Hästmyr, Hästmyr, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>496237</v>
+        <v>496283</v>
       </c>
       <c r="R19" t="n">
-        <v>6780285</v>
+        <v>6779932</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2624,7 +2620,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2634,7 +2630,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Bohål I Björk</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2643,19 +2644,18 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Jakob Bowers</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Jakob Bowers</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2665,7 +2665,7 @@
         <v>128838007</v>
       </c>
       <c r="B20" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2781,7 +2781,7 @@
         <v>128838020</v>
       </c>
       <c r="B21" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2885,32 +2885,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128837996</v>
+        <v>128838021</v>
       </c>
       <c r="B22" t="n">
-        <v>79735</v>
+        <v>92789</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2920,10 +2920,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>496236</v>
+        <v>496349</v>
       </c>
       <c r="R22" t="n">
-        <v>6779955</v>
+        <v>6779557</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2965,7 +2965,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2974,7 +2974,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2993,10 +2992,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128838041</v>
+        <v>128837996</v>
       </c>
       <c r="B23" t="n">
-        <v>57713</v>
+        <v>79739</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3004,21 +3003,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3028,10 +3027,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>496237</v>
+        <v>496236</v>
       </c>
       <c r="R23" t="n">
-        <v>6780345</v>
+        <v>6779955</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3063,7 +3062,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3073,7 +3072,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3082,6 +3081,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3100,32 +3100,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128838021</v>
+        <v>128838041</v>
       </c>
       <c r="B24" t="n">
-        <v>92784</v>
+        <v>57713</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3135,10 +3135,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>496349</v>
+        <v>496237</v>
       </c>
       <c r="R24" t="n">
-        <v>6779557</v>
+        <v>6780345</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3170,7 +3170,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3180,7 +3180,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3210,7 +3210,7 @@
         <v>128838014</v>
       </c>
       <c r="B25" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3317,7 +3317,7 @@
         <v>128837995</v>
       </c>
       <c r="B26" t="n">
-        <v>90526</v>
+        <v>90531</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3425,7 +3425,7 @@
         <v>128837997</v>
       </c>
       <c r="B27" t="n">
-        <v>79735</v>
+        <v>79739</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3760,7 +3760,7 @@
         <v>128838019</v>
       </c>
       <c r="B30" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3867,7 +3867,7 @@
         <v>128838015</v>
       </c>
       <c r="B31" t="n">
-        <v>79116</v>
+        <v>79120</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3971,32 +3971,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128838043</v>
+        <v>128838013</v>
       </c>
       <c r="B32" t="n">
-        <v>8450</v>
+        <v>79120</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4006,10 +4006,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>496351</v>
+        <v>496280</v>
       </c>
       <c r="R32" t="n">
-        <v>6780109</v>
+        <v>6779962</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4041,7 +4041,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4051,7 +4051,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4078,32 +4078,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128838013</v>
+        <v>128838043</v>
       </c>
       <c r="B33" t="n">
-        <v>79116</v>
+        <v>8450</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4113,10 +4113,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>496280</v>
+        <v>496351</v>
       </c>
       <c r="R33" t="n">
-        <v>6779962</v>
+        <v>6780109</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4148,7 +4148,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4158,7 +4158,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD33" t="b">

--- a/artfynd/A 39682-2025 artfynd.xlsx
+++ b/artfynd/A 39682-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128838055</v>
       </c>
       <c r="B2" t="n">
-        <v>92789</v>
+        <v>92794</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>128838023</v>
       </c>
       <c r="B4" t="n">
-        <v>92789</v>
+        <v>92794</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
         <v>128838052</v>
       </c>
       <c r="B18" t="n">
-        <v>92789</v>
+        <v>92794</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2888,7 +2888,7 @@
         <v>128838021</v>
       </c>
       <c r="B22" t="n">
-        <v>92789</v>
+        <v>92794</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2992,10 +2992,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128837996</v>
+        <v>128838041</v>
       </c>
       <c r="B23" t="n">
-        <v>79739</v>
+        <v>57713</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3003,21 +3003,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3027,10 +3027,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>496236</v>
+        <v>496237</v>
       </c>
       <c r="R23" t="n">
-        <v>6779955</v>
+        <v>6780345</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3062,7 +3062,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3072,7 +3072,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3081,7 +3081,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3100,10 +3099,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128838041</v>
+        <v>128837996</v>
       </c>
       <c r="B24" t="n">
-        <v>57713</v>
+        <v>79739</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3111,21 +3110,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3135,10 +3134,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>496237</v>
+        <v>496236</v>
       </c>
       <c r="R24" t="n">
-        <v>6780345</v>
+        <v>6779955</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3170,7 +3169,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3180,7 +3179,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3189,6 +3188,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3317,7 +3317,7 @@
         <v>128837995</v>
       </c>
       <c r="B26" t="n">
-        <v>90531</v>
+        <v>90536</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3530,53 +3530,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128838328</v>
+        <v>128838042</v>
       </c>
       <c r="B28" t="n">
-        <v>57716</v>
+        <v>8450</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Hästmyr, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>496327</v>
+        <v>496270</v>
       </c>
       <c r="R28" t="n">
-        <v>6779866</v>
+        <v>6780214</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3608,7 +3600,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3618,12 +3610,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:05</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack högt på tall</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3650,45 +3637,53 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128838042</v>
+        <v>128838328</v>
       </c>
       <c r="B29" t="n">
-        <v>8450</v>
+        <v>57716</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Hästmyr, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>496270</v>
+        <v>496327</v>
       </c>
       <c r="R29" t="n">
-        <v>6780214</v>
+        <v>6779866</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3720,7 +3715,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3730,7 +3725,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack högt på tall</t>
         </is>
       </c>
       <c r="AD29" t="b">

--- a/artfynd/A 39682-2025 artfynd.xlsx
+++ b/artfynd/A 39682-2025 artfynd.xlsx
@@ -1232,53 +1232,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128838001</v>
+        <v>128838005</v>
       </c>
       <c r="B7" t="n">
-        <v>57716</v>
+        <v>43979</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>101735</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hästmyr, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>496347</v>
+        <v>496344</v>
       </c>
       <c r="R7" t="n">
-        <v>6779846</v>
+        <v>6779645</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1310,7 +1302,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,12 +1312,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:21</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack högt upp på tall</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1334,6 +1321,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1352,45 +1340,53 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128838005</v>
+        <v>128838001</v>
       </c>
       <c r="B8" t="n">
-        <v>43979</v>
+        <v>57716</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>101735</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hästmyr, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>496344</v>
+        <v>496347</v>
       </c>
       <c r="R8" t="n">
-        <v>6779645</v>
+        <v>6779846</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1422,7 +1418,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1428,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack högt upp på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1441,7 +1442,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1460,32 +1460,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128838047</v>
+        <v>128838045</v>
       </c>
       <c r="B9" t="n">
-        <v>79120</v>
+        <v>43979</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>101735</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1495,10 +1495,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>496281</v>
+        <v>496345</v>
       </c>
       <c r="R9" t="n">
-        <v>6780389</v>
+        <v>6780049</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1540,7 +1540,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1549,6 +1549,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1567,7 +1568,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128838011</v>
+        <v>128838047</v>
       </c>
       <c r="B10" t="n">
         <v>79120</v>
@@ -1602,10 +1603,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>496295</v>
+        <v>496281</v>
       </c>
       <c r="R10" t="n">
-        <v>6779954</v>
+        <v>6780389</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1637,7 +1638,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1647,7 +1648,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1674,32 +1675,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128838045</v>
+        <v>128838011</v>
       </c>
       <c r="B11" t="n">
-        <v>43979</v>
+        <v>79120</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>101735</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1709,10 +1710,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>496345</v>
+        <v>496295</v>
       </c>
       <c r="R11" t="n">
-        <v>6780049</v>
+        <v>6779954</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1744,7 +1745,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1754,7 +1755,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1763,7 +1764,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -2992,10 +2992,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128838041</v>
+        <v>128837996</v>
       </c>
       <c r="B23" t="n">
-        <v>57713</v>
+        <v>79739</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3003,21 +3003,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3027,10 +3027,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>496237</v>
+        <v>496236</v>
       </c>
       <c r="R23" t="n">
-        <v>6780345</v>
+        <v>6779955</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3062,7 +3062,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3072,7 +3072,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3081,6 +3081,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3099,10 +3100,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128837996</v>
+        <v>128838041</v>
       </c>
       <c r="B24" t="n">
-        <v>79739</v>
+        <v>57713</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3110,21 +3111,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3134,10 +3135,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>496236</v>
+        <v>496237</v>
       </c>
       <c r="R24" t="n">
-        <v>6779955</v>
+        <v>6780345</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3169,7 +3170,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3179,7 +3180,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3188,7 +3189,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3530,45 +3530,53 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128838042</v>
+        <v>128838328</v>
       </c>
       <c r="B28" t="n">
-        <v>8450</v>
+        <v>57716</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Hästmyr, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>496270</v>
+        <v>496327</v>
       </c>
       <c r="R28" t="n">
-        <v>6780214</v>
+        <v>6779866</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3600,7 +3608,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3610,7 +3618,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack högt på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3637,53 +3650,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128838328</v>
+        <v>128838042</v>
       </c>
       <c r="B29" t="n">
-        <v>57716</v>
+        <v>8450</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Hästmyr, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>496327</v>
+        <v>496270</v>
       </c>
       <c r="R29" t="n">
-        <v>6779866</v>
+        <v>6780214</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3715,7 +3720,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3725,12 +3730,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:05</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack högt på tall</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD29" t="b">

--- a/artfynd/A 39682-2025 artfynd.xlsx
+++ b/artfynd/A 39682-2025 artfynd.xlsx
@@ -675,45 +675,53 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128838055</v>
+        <v>128838036</v>
       </c>
       <c r="B2" t="n">
-        <v>92794</v>
+        <v>57716</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hästmyr, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>496351</v>
+        <v>496264</v>
       </c>
       <c r="R2" t="n">
-        <v>6780081</v>
+        <v>6780257</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +763,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack högt på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,53 +795,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128838036</v>
+        <v>128838055</v>
       </c>
       <c r="B3" t="n">
-        <v>57716</v>
+        <v>92794</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hästmyr, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>496264</v>
+        <v>496351</v>
       </c>
       <c r="R3" t="n">
-        <v>6780257</v>
+        <v>6780081</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,7 +865,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -870,12 +875,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:43</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack högt på tall</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -1232,45 +1232,53 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128838005</v>
+        <v>128838001</v>
       </c>
       <c r="B7" t="n">
-        <v>43979</v>
+        <v>57716</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>101735</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hästmyr, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>496344</v>
+        <v>496347</v>
       </c>
       <c r="R7" t="n">
-        <v>6779645</v>
+        <v>6779846</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1302,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1312,7 +1320,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack högt upp på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1321,7 +1334,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1340,53 +1352,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128838001</v>
+        <v>128838005</v>
       </c>
       <c r="B8" t="n">
-        <v>57716</v>
+        <v>43979</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>101735</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hästmyr, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>496347</v>
+        <v>496344</v>
       </c>
       <c r="R8" t="n">
-        <v>6779846</v>
+        <v>6779645</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1418,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1428,12 +1432,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:21</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack högt upp på tall</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1442,6 +1441,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1460,32 +1460,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128838045</v>
+        <v>128838047</v>
       </c>
       <c r="B9" t="n">
-        <v>43979</v>
+        <v>79120</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>101735</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1495,10 +1495,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>496345</v>
+        <v>496281</v>
       </c>
       <c r="R9" t="n">
-        <v>6780049</v>
+        <v>6780389</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1540,7 +1540,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1549,7 +1549,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1568,7 +1567,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128838047</v>
+        <v>128838011</v>
       </c>
       <c r="B10" t="n">
         <v>79120</v>
@@ -1603,10 +1602,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>496281</v>
+        <v>496295</v>
       </c>
       <c r="R10" t="n">
-        <v>6780389</v>
+        <v>6779954</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1638,7 +1637,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1648,7 +1647,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1675,32 +1674,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128838011</v>
+        <v>128838045</v>
       </c>
       <c r="B11" t="n">
-        <v>79120</v>
+        <v>43979</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>101735</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1710,10 +1709,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>496295</v>
+        <v>496345</v>
       </c>
       <c r="R11" t="n">
-        <v>6779954</v>
+        <v>6780049</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1745,7 +1744,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1755,7 +1754,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1764,6 +1763,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -2885,32 +2885,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128838021</v>
+        <v>128837996</v>
       </c>
       <c r="B22" t="n">
-        <v>92794</v>
+        <v>79739</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2920,10 +2920,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>496349</v>
+        <v>496236</v>
       </c>
       <c r="R22" t="n">
-        <v>6779557</v>
+        <v>6779955</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2965,7 +2965,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2974,6 +2974,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2992,10 +2993,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128837996</v>
+        <v>128838041</v>
       </c>
       <c r="B23" t="n">
-        <v>79739</v>
+        <v>57713</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3003,21 +3004,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3027,10 +3028,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>496236</v>
+        <v>496237</v>
       </c>
       <c r="R23" t="n">
-        <v>6779955</v>
+        <v>6780345</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3062,7 +3063,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3072,7 +3073,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3081,7 +3082,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3100,32 +3100,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128838041</v>
+        <v>128838021</v>
       </c>
       <c r="B24" t="n">
-        <v>57713</v>
+        <v>92794</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3135,10 +3135,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>496237</v>
+        <v>496349</v>
       </c>
       <c r="R24" t="n">
-        <v>6780345</v>
+        <v>6779557</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3170,7 +3170,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3180,7 +3180,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3530,53 +3530,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128838328</v>
+        <v>128838042</v>
       </c>
       <c r="B28" t="n">
-        <v>57716</v>
+        <v>8450</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Hästmyr, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>496327</v>
+        <v>496270</v>
       </c>
       <c r="R28" t="n">
-        <v>6779866</v>
+        <v>6780214</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3608,7 +3600,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3618,12 +3610,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:05</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack högt på tall</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3650,45 +3637,53 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128838042</v>
+        <v>128838328</v>
       </c>
       <c r="B29" t="n">
-        <v>8450</v>
+        <v>57716</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Hästmyr, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>496270</v>
+        <v>496327</v>
       </c>
       <c r="R29" t="n">
-        <v>6780214</v>
+        <v>6779866</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3720,7 +3715,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3730,7 +3725,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack högt på tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3971,32 +3971,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128838013</v>
+        <v>128838043</v>
       </c>
       <c r="B32" t="n">
-        <v>79120</v>
+        <v>8450</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4006,10 +4006,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>496280</v>
+        <v>496351</v>
       </c>
       <c r="R32" t="n">
-        <v>6779962</v>
+        <v>6780109</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4041,7 +4041,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4051,7 +4051,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4078,32 +4078,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128838043</v>
+        <v>128838013</v>
       </c>
       <c r="B33" t="n">
-        <v>8450</v>
+        <v>79120</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4113,10 +4113,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>496351</v>
+        <v>496280</v>
       </c>
       <c r="R33" t="n">
-        <v>6780109</v>
+        <v>6779962</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4148,7 +4148,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4158,7 +4158,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD33" t="b">

--- a/artfynd/A 39682-2025 artfynd.xlsx
+++ b/artfynd/A 39682-2025 artfynd.xlsx
@@ -675,53 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128838036</v>
+        <v>128838055</v>
       </c>
       <c r="B2" t="n">
-        <v>57716</v>
+        <v>92798</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hästmyr, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>496264</v>
+        <v>496351</v>
       </c>
       <c r="R2" t="n">
-        <v>6780257</v>
+        <v>6780081</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,12 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:43</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack högt på tall</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,45 +782,53 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128838055</v>
+        <v>128838036</v>
       </c>
       <c r="B3" t="n">
-        <v>92794</v>
+        <v>57720</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hästmyr, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>496351</v>
+        <v>496264</v>
       </c>
       <c r="R3" t="n">
-        <v>6780081</v>
+        <v>6780257</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -875,7 +870,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack högt på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,7 +905,7 @@
         <v>128838023</v>
       </c>
       <c r="B4" t="n">
-        <v>92794</v>
+        <v>92798</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
         <v>128838012</v>
       </c>
       <c r="B5" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
         <v>128838010</v>
       </c>
       <c r="B6" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>128838001</v>
       </c>
       <c r="B7" t="n">
-        <v>57716</v>
+        <v>57720</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>128838005</v>
       </c>
       <c r="B8" t="n">
-        <v>43979</v>
+        <v>43980</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1460,32 +1460,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128838047</v>
+        <v>128838045</v>
       </c>
       <c r="B9" t="n">
-        <v>79120</v>
+        <v>43980</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>101735</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1495,10 +1495,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>496281</v>
+        <v>496345</v>
       </c>
       <c r="R9" t="n">
-        <v>6780389</v>
+        <v>6780049</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1540,7 +1540,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1549,6 +1549,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1567,10 +1568,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128838011</v>
+        <v>128838047</v>
       </c>
       <c r="B10" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1602,10 +1603,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>496295</v>
+        <v>496281</v>
       </c>
       <c r="R10" t="n">
-        <v>6779954</v>
+        <v>6780389</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1637,7 +1638,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1647,7 +1648,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1674,32 +1675,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128838045</v>
+        <v>128838011</v>
       </c>
       <c r="B11" t="n">
-        <v>43979</v>
+        <v>79124</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>101735</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1709,10 +1710,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>496345</v>
+        <v>496295</v>
       </c>
       <c r="R11" t="n">
-        <v>6780049</v>
+        <v>6779954</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1744,7 +1745,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1754,7 +1755,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1763,7 +1764,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1782,10 +1782,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128838046</v>
+        <v>128838048</v>
       </c>
       <c r="B12" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1811,19 +1811,16 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hästmyr, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>496348</v>
+        <v>496271</v>
       </c>
       <c r="R12" t="n">
-        <v>6780084</v>
+        <v>6780378</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1855,7 +1852,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1865,12 +1862,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:51</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1879,7 +1871,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1898,10 +1889,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128838048</v>
+        <v>128838046</v>
       </c>
       <c r="B13" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1927,16 +1918,19 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hästmyr, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>496271</v>
+        <v>496348</v>
       </c>
       <c r="R13" t="n">
-        <v>6780378</v>
+        <v>6780084</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1968,7 +1962,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1978,7 +1972,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1987,6 +1986,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2005,10 +2005,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128838049</v>
+        <v>128838050</v>
       </c>
       <c r="B14" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2040,10 +2040,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>496350</v>
+        <v>496259</v>
       </c>
       <c r="R14" t="n">
-        <v>6780093</v>
+        <v>6780405</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2085,7 +2085,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2115,7 +2115,7 @@
         <v>128838009</v>
       </c>
       <c r="B15" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2228,10 +2228,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128838050</v>
+        <v>128838049</v>
       </c>
       <c r="B16" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2263,10 +2263,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>496259</v>
+        <v>496350</v>
       </c>
       <c r="R16" t="n">
-        <v>6780405</v>
+        <v>6780093</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2308,7 +2308,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2338,7 +2338,7 @@
         <v>128838017</v>
       </c>
       <c r="B17" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2442,48 +2442,48 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128838052</v>
+        <v>128842520</v>
       </c>
       <c r="B18" t="n">
-        <v>92794</v>
+        <v>57720</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Hästmyr, Dlr</t>
+          <t>Hästmyr, Hästmyr, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>496237</v>
+        <v>496283</v>
       </c>
       <c r="R18" t="n">
-        <v>6780285</v>
+        <v>6779932</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2522,7 +2522,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Bohål I Björk</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2531,67 +2536,66 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Jakob Bowers</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Jakob Bowers</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128842520</v>
+        <v>128838052</v>
       </c>
       <c r="B19" t="n">
-        <v>57716</v>
+        <v>92798</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Hästmyr, Hästmyr, Dlr</t>
+          <t>Hästmyr, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>496283</v>
+        <v>496237</v>
       </c>
       <c r="R19" t="n">
-        <v>6779932</v>
+        <v>6780285</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2620,7 +2624,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2630,12 +2634,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Bohål I Björk</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2644,18 +2643,19 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Jakob Bowers</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Jakob Bowers</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2665,7 +2665,7 @@
         <v>128838007</v>
       </c>
       <c r="B20" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2781,7 +2781,7 @@
         <v>128838020</v>
       </c>
       <c r="B21" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2885,10 +2885,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128837996</v>
+        <v>128838041</v>
       </c>
       <c r="B22" t="n">
-        <v>79739</v>
+        <v>57717</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2896,21 +2896,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2920,10 +2920,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>496236</v>
+        <v>496237</v>
       </c>
       <c r="R22" t="n">
-        <v>6779955</v>
+        <v>6780345</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2965,7 +2965,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2974,7 +2974,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2993,32 +2992,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128838041</v>
+        <v>128838021</v>
       </c>
       <c r="B23" t="n">
-        <v>57713</v>
+        <v>92798</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3028,10 +3027,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>496237</v>
+        <v>496349</v>
       </c>
       <c r="R23" t="n">
-        <v>6780345</v>
+        <v>6779557</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3063,7 +3062,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3073,7 +3072,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3100,32 +3099,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128838021</v>
+        <v>128837996</v>
       </c>
       <c r="B24" t="n">
-        <v>92794</v>
+        <v>79743</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3135,10 +3134,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>496349</v>
+        <v>496236</v>
       </c>
       <c r="R24" t="n">
-        <v>6779557</v>
+        <v>6779955</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3170,7 +3169,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3180,7 +3179,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3189,6 +3188,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3210,7 +3210,7 @@
         <v>128838014</v>
       </c>
       <c r="B25" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3317,7 +3317,7 @@
         <v>128837995</v>
       </c>
       <c r="B26" t="n">
-        <v>90536</v>
+        <v>90540</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3425,7 +3425,7 @@
         <v>128837997</v>
       </c>
       <c r="B27" t="n">
-        <v>79739</v>
+        <v>79743</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3530,45 +3530,53 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128838042</v>
+        <v>128838328</v>
       </c>
       <c r="B28" t="n">
-        <v>8450</v>
+        <v>57720</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Hästmyr, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>496270</v>
+        <v>496327</v>
       </c>
       <c r="R28" t="n">
-        <v>6780214</v>
+        <v>6779866</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3600,7 +3608,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3610,7 +3618,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack högt på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3637,53 +3650,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128838328</v>
+        <v>128838042</v>
       </c>
       <c r="B29" t="n">
-        <v>57716</v>
+        <v>8450</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Hästmyr, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>496327</v>
+        <v>496270</v>
       </c>
       <c r="R29" t="n">
-        <v>6779866</v>
+        <v>6780214</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3715,7 +3720,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3725,12 +3730,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:05</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack högt på tall</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3760,7 +3760,7 @@
         <v>128838019</v>
       </c>
       <c r="B30" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3867,7 +3867,7 @@
         <v>128838015</v>
       </c>
       <c r="B31" t="n">
-        <v>79120</v>
+        <v>79124</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3971,32 +3971,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128838043</v>
+        <v>128838013</v>
       </c>
       <c r="B32" t="n">
-        <v>8450</v>
+        <v>79124</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4006,10 +4006,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>496351</v>
+        <v>496280</v>
       </c>
       <c r="R32" t="n">
-        <v>6780109</v>
+        <v>6779962</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4041,7 +4041,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4051,7 +4051,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4078,32 +4078,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128838013</v>
+        <v>128838043</v>
       </c>
       <c r="B33" t="n">
-        <v>79120</v>
+        <v>8450</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4113,10 +4113,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>496280</v>
+        <v>496351</v>
       </c>
       <c r="R33" t="n">
-        <v>6779962</v>
+        <v>6780109</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4148,7 +4148,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4158,7 +4158,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD33" t="b">

--- a/artfynd/A 39682-2025 artfynd.xlsx
+++ b/artfynd/A 39682-2025 artfynd.xlsx
@@ -1460,32 +1460,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128838045</v>
+        <v>128838047</v>
       </c>
       <c r="B9" t="n">
-        <v>43980</v>
+        <v>79124</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>101735</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1495,10 +1495,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>496345</v>
+        <v>496281</v>
       </c>
       <c r="R9" t="n">
-        <v>6780049</v>
+        <v>6780389</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1540,7 +1540,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1549,7 +1549,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1568,32 +1567,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128838047</v>
+        <v>128838045</v>
       </c>
       <c r="B10" t="n">
-        <v>79124</v>
+        <v>43980</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>101735</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1603,10 +1602,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>496281</v>
+        <v>496345</v>
       </c>
       <c r="R10" t="n">
-        <v>6780389</v>
+        <v>6780049</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1638,7 +1637,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1648,7 +1647,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1657,6 +1656,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1782,7 +1782,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128838048</v>
+        <v>128838046</v>
       </c>
       <c r="B12" t="n">
         <v>79124</v>
@@ -1811,16 +1811,19 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hästmyr, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>496271</v>
+        <v>496348</v>
       </c>
       <c r="R12" t="n">
-        <v>6780378</v>
+        <v>6780084</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1852,7 +1855,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1862,7 +1865,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1871,6 +1879,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1889,7 +1898,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128838046</v>
+        <v>128838048</v>
       </c>
       <c r="B13" t="n">
         <v>79124</v>
@@ -1918,19 +1927,16 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hästmyr, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>496348</v>
+        <v>496271</v>
       </c>
       <c r="R13" t="n">
-        <v>6780084</v>
+        <v>6780378</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1962,7 +1968,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1972,12 +1978,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:51</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1986,7 +1987,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2005,7 +2005,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128838050</v>
+        <v>128838049</v>
       </c>
       <c r="B14" t="n">
         <v>79124</v>
@@ -2040,10 +2040,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>496259</v>
+        <v>496350</v>
       </c>
       <c r="R14" t="n">
-        <v>6780405</v>
+        <v>6780093</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2085,7 +2085,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2228,7 +2228,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128838049</v>
+        <v>128838050</v>
       </c>
       <c r="B16" t="n">
         <v>79124</v>
@@ -2263,10 +2263,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>496350</v>
+        <v>496259</v>
       </c>
       <c r="R16" t="n">
-        <v>6780093</v>
+        <v>6780405</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2308,7 +2308,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2442,48 +2442,48 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128842520</v>
+        <v>128838052</v>
       </c>
       <c r="B18" t="n">
-        <v>57720</v>
+        <v>92798</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Hästmyr, Hästmyr, Dlr</t>
+          <t>Hästmyr, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>496283</v>
+        <v>496237</v>
       </c>
       <c r="R18" t="n">
-        <v>6779932</v>
+        <v>6780285</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2522,12 +2522,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Bohål I Björk</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2536,66 +2531,67 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Jakob Bowers</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Jakob Bowers</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128838052</v>
+        <v>128842520</v>
       </c>
       <c r="B19" t="n">
-        <v>92798</v>
+        <v>57720</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Hästmyr, Dlr</t>
+          <t>Hästmyr, Hästmyr, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>496237</v>
+        <v>496283</v>
       </c>
       <c r="R19" t="n">
-        <v>6780285</v>
+        <v>6779932</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2624,7 +2620,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2634,7 +2630,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Bohål I Björk</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2643,19 +2644,18 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Jakob Bowers</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Jakob Bowers</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2885,32 +2885,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128838041</v>
+        <v>128838021</v>
       </c>
       <c r="B22" t="n">
-        <v>57717</v>
+        <v>92798</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2920,10 +2920,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>496237</v>
+        <v>496349</v>
       </c>
       <c r="R22" t="n">
-        <v>6780345</v>
+        <v>6779557</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2965,7 +2965,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2992,32 +2992,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128838021</v>
+        <v>128837996</v>
       </c>
       <c r="B23" t="n">
-        <v>92798</v>
+        <v>79743</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3027,10 +3027,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>496349</v>
+        <v>496236</v>
       </c>
       <c r="R23" t="n">
-        <v>6779557</v>
+        <v>6779955</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3062,7 +3062,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3072,7 +3072,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3081,6 +3081,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3099,10 +3100,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128837996</v>
+        <v>128838041</v>
       </c>
       <c r="B24" t="n">
-        <v>79743</v>
+        <v>57717</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3110,21 +3111,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3134,10 +3135,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>496236</v>
+        <v>496237</v>
       </c>
       <c r="R24" t="n">
-        <v>6779955</v>
+        <v>6780345</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3169,7 +3170,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3179,7 +3180,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3188,7 +3189,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 39682-2025 artfynd.xlsx
+++ b/artfynd/A 39682-2025 artfynd.xlsx
@@ -1567,32 +1567,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128838045</v>
+        <v>128838011</v>
       </c>
       <c r="B10" t="n">
-        <v>43980</v>
+        <v>79124</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>101735</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1602,10 +1602,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>496345</v>
+        <v>496295</v>
       </c>
       <c r="R10" t="n">
-        <v>6780049</v>
+        <v>6779954</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1656,7 +1656,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1675,32 +1674,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128838011</v>
+        <v>128838045</v>
       </c>
       <c r="B11" t="n">
-        <v>79124</v>
+        <v>43980</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>101735</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1710,10 +1709,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>496295</v>
+        <v>496345</v>
       </c>
       <c r="R11" t="n">
-        <v>6779954</v>
+        <v>6780049</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1745,7 +1744,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1755,7 +1754,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1764,6 +1763,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -2442,48 +2442,48 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128838052</v>
+        <v>128842520</v>
       </c>
       <c r="B18" t="n">
-        <v>92798</v>
+        <v>57720</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Hästmyr, Dlr</t>
+          <t>Hästmyr, Hästmyr, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>496237</v>
+        <v>496283</v>
       </c>
       <c r="R18" t="n">
-        <v>6780285</v>
+        <v>6779932</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2522,7 +2522,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Bohål I Björk</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2531,67 +2536,66 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Jakob Bowers</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Jakob Bowers</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128842520</v>
+        <v>128838052</v>
       </c>
       <c r="B19" t="n">
-        <v>57720</v>
+        <v>92798</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Hästmyr, Hästmyr, Dlr</t>
+          <t>Hästmyr, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>496283</v>
+        <v>496237</v>
       </c>
       <c r="R19" t="n">
-        <v>6779932</v>
+        <v>6780285</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2620,7 +2624,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2630,12 +2634,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Bohål I Björk</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2644,18 +2643,19 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Jakob Bowers</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Jakob Bowers</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -3530,53 +3530,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128838328</v>
+        <v>128838042</v>
       </c>
       <c r="B28" t="n">
-        <v>57720</v>
+        <v>8450</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Hästmyr, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>496327</v>
+        <v>496270</v>
       </c>
       <c r="R28" t="n">
-        <v>6779866</v>
+        <v>6780214</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3608,7 +3600,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3618,12 +3610,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:05</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack högt på tall</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3650,45 +3637,53 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128838042</v>
+        <v>128838328</v>
       </c>
       <c r="B29" t="n">
-        <v>8450</v>
+        <v>57720</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Hästmyr, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>496270</v>
+        <v>496327</v>
       </c>
       <c r="R29" t="n">
-        <v>6780214</v>
+        <v>6779866</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3720,7 +3715,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3730,7 +3725,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack högt på tall</t>
         </is>
       </c>
       <c r="AD29" t="b">

--- a/artfynd/A 39682-2025 artfynd.xlsx
+++ b/artfynd/A 39682-2025 artfynd.xlsx
@@ -675,45 +675,53 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128838055</v>
+        <v>128838036</v>
       </c>
       <c r="B2" t="n">
-        <v>92798</v>
+        <v>57723</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hästmyr, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>496351</v>
+        <v>496264</v>
       </c>
       <c r="R2" t="n">
-        <v>6780081</v>
+        <v>6780257</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +763,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack högt på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,53 +795,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128838036</v>
+        <v>128838055</v>
       </c>
       <c r="B3" t="n">
-        <v>57720</v>
+        <v>92803</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hästmyr, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>496264</v>
+        <v>496351</v>
       </c>
       <c r="R3" t="n">
-        <v>6780257</v>
+        <v>6780081</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,7 +865,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -870,12 +875,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:43</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack högt på tall</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,7 +905,7 @@
         <v>128838023</v>
       </c>
       <c r="B4" t="n">
-        <v>92798</v>
+        <v>92803</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
         <v>128838012</v>
       </c>
       <c r="B5" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
         <v>128838010</v>
       </c>
       <c r="B6" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>128838001</v>
       </c>
       <c r="B7" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1355,7 +1355,7 @@
         <v>128838005</v>
       </c>
       <c r="B8" t="n">
-        <v>43980</v>
+        <v>43982</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         <v>128838047</v>
       </c>
       <c r="B9" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         <v>128838011</v>
       </c>
       <c r="B10" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1677,7 +1677,7 @@
         <v>128838045</v>
       </c>
       <c r="B11" t="n">
-        <v>43980</v>
+        <v>43982</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         <v>128838046</v>
       </c>
       <c r="B12" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         <v>128838048</v>
       </c>
       <c r="B13" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2008,7 +2008,7 @@
         <v>128838049</v>
       </c>
       <c r="B14" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2115,7 +2115,7 @@
         <v>128838009</v>
       </c>
       <c r="B15" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
         <v>128838050</v>
       </c>
       <c r="B16" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>128838017</v>
       </c>
       <c r="B17" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2442,48 +2442,48 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128842520</v>
+        <v>128838052</v>
       </c>
       <c r="B18" t="n">
-        <v>57720</v>
+        <v>92803</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Hästmyr, Hästmyr, Dlr</t>
+          <t>Hästmyr, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>496283</v>
+        <v>496237</v>
       </c>
       <c r="R18" t="n">
-        <v>6779932</v>
+        <v>6780285</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2522,12 +2522,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Bohål I Björk</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2536,66 +2531,67 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Jakob Bowers</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Jakob Bowers</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128838052</v>
+        <v>128842520</v>
       </c>
       <c r="B19" t="n">
-        <v>92798</v>
+        <v>57723</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Hästmyr, Dlr</t>
+          <t>Hästmyr, Hästmyr, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>496237</v>
+        <v>496283</v>
       </c>
       <c r="R19" t="n">
-        <v>6780285</v>
+        <v>6779932</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2624,7 +2620,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2634,7 +2630,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Bohål I Björk</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2643,19 +2644,18 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Jakob Bowers</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Jakob Bowers</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2665,7 +2665,7 @@
         <v>128838007</v>
       </c>
       <c r="B20" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2781,7 +2781,7 @@
         <v>128838020</v>
       </c>
       <c r="B21" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2885,32 +2885,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128838021</v>
+        <v>128838041</v>
       </c>
       <c r="B22" t="n">
-        <v>92798</v>
+        <v>57720</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2920,10 +2920,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>496349</v>
+        <v>496237</v>
       </c>
       <c r="R22" t="n">
-        <v>6779557</v>
+        <v>6780345</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2965,7 +2965,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2992,32 +2992,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128837996</v>
+        <v>128838021</v>
       </c>
       <c r="B23" t="n">
-        <v>79743</v>
+        <v>92803</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3027,10 +3027,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>496236</v>
+        <v>496349</v>
       </c>
       <c r="R23" t="n">
-        <v>6779955</v>
+        <v>6779557</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3062,7 +3062,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3072,7 +3072,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3081,7 +3081,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3100,10 +3099,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128838041</v>
+        <v>128837996</v>
       </c>
       <c r="B24" t="n">
-        <v>57717</v>
+        <v>79648</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3111,21 +3110,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3135,10 +3134,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>496237</v>
+        <v>496236</v>
       </c>
       <c r="R24" t="n">
-        <v>6780345</v>
+        <v>6779955</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3170,7 +3169,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3180,7 +3179,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3189,6 +3188,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3210,7 +3210,7 @@
         <v>128838014</v>
       </c>
       <c r="B25" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3317,7 +3317,7 @@
         <v>128837995</v>
       </c>
       <c r="B26" t="n">
-        <v>90540</v>
+        <v>90545</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3425,7 +3425,7 @@
         <v>128837997</v>
       </c>
       <c r="B27" t="n">
-        <v>79743</v>
+        <v>79648</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3530,45 +3530,53 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128838042</v>
+        <v>128838328</v>
       </c>
       <c r="B28" t="n">
-        <v>8450</v>
+        <v>57723</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Hästmyr, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>496270</v>
+        <v>496327</v>
       </c>
       <c r="R28" t="n">
-        <v>6780214</v>
+        <v>6779866</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3600,7 +3608,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3610,7 +3618,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack högt på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3637,53 +3650,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128838328</v>
+        <v>128838042</v>
       </c>
       <c r="B29" t="n">
-        <v>57720</v>
+        <v>8450</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Hästmyr, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>496327</v>
+        <v>496270</v>
       </c>
       <c r="R29" t="n">
-        <v>6779866</v>
+        <v>6780214</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3715,7 +3720,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3725,12 +3730,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:05</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack högt på tall</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3760,7 +3760,7 @@
         <v>128838019</v>
       </c>
       <c r="B30" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3867,7 +3867,7 @@
         <v>128838015</v>
       </c>
       <c r="B31" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3974,7 +3974,7 @@
         <v>128838013</v>
       </c>
       <c r="B32" t="n">
-        <v>79124</v>
+        <v>79029</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 39682-2025 artfynd.xlsx
+++ b/artfynd/A 39682-2025 artfynd.xlsx
@@ -2885,32 +2885,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128837996</v>
+        <v>128838021</v>
       </c>
       <c r="B22" t="n">
-        <v>79653</v>
+        <v>92811</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2920,10 +2920,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>496236</v>
+        <v>496349</v>
       </c>
       <c r="R22" t="n">
-        <v>6779955</v>
+        <v>6779557</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2965,7 +2965,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2974,7 +2974,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2993,32 +2992,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128838021</v>
+        <v>128837996</v>
       </c>
       <c r="B23" t="n">
-        <v>92811</v>
+        <v>79653</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3028,10 +3027,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>496349</v>
+        <v>496236</v>
       </c>
       <c r="R23" t="n">
-        <v>6779557</v>
+        <v>6779955</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3063,7 +3062,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3073,7 +3072,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3082,6 +3081,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 39682-2025 artfynd.xlsx
+++ b/artfynd/A 39682-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128838055</v>
       </c>
       <c r="B2" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>128838023</v>
       </c>
       <c r="B4" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1232,53 +1232,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128838001</v>
+        <v>128838005</v>
       </c>
       <c r="B7" t="n">
-        <v>57723</v>
+        <v>43982</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>101735</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hästmyr, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>496347</v>
+        <v>496344</v>
       </c>
       <c r="R7" t="n">
-        <v>6779846</v>
+        <v>6779645</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1310,7 +1302,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,12 +1312,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:21</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack högt upp på tall</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1334,6 +1321,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1352,45 +1340,53 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128838005</v>
+        <v>128838001</v>
       </c>
       <c r="B8" t="n">
-        <v>43982</v>
+        <v>57723</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>101735</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hästmyr, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>496344</v>
+        <v>496347</v>
       </c>
       <c r="R8" t="n">
-        <v>6779645</v>
+        <v>6779846</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1422,7 +1418,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1428,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Ringhack högt upp på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1441,7 +1442,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -2442,48 +2442,48 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128838052</v>
+        <v>128842520</v>
       </c>
       <c r="B18" t="n">
-        <v>92811</v>
+        <v>57723</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Hästmyr, Dlr</t>
+          <t>Hästmyr, Hästmyr, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>496237</v>
+        <v>496283</v>
       </c>
       <c r="R18" t="n">
-        <v>6780285</v>
+        <v>6779932</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2522,7 +2522,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Bohål I Björk</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2531,67 +2536,66 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Jakob Bowers</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Jakob Bowers</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128842520</v>
+        <v>128838052</v>
       </c>
       <c r="B19" t="n">
-        <v>57723</v>
+        <v>92816</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Hästmyr, Hästmyr, Dlr</t>
+          <t>Hästmyr, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>496283</v>
+        <v>496237</v>
       </c>
       <c r="R19" t="n">
-        <v>6779932</v>
+        <v>6780285</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2620,7 +2624,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2630,12 +2634,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Bohål I Björk</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2644,18 +2643,19 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Jakob Bowers</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Jakob Bowers</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2885,32 +2885,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128838021</v>
+        <v>128837996</v>
       </c>
       <c r="B22" t="n">
-        <v>92811</v>
+        <v>79653</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2920,10 +2920,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>496349</v>
+        <v>496236</v>
       </c>
       <c r="R22" t="n">
-        <v>6779557</v>
+        <v>6779955</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2965,7 +2965,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2974,6 +2974,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2992,32 +2993,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128837996</v>
+        <v>128838021</v>
       </c>
       <c r="B23" t="n">
-        <v>79653</v>
+        <v>92816</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3027,10 +3028,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>496236</v>
+        <v>496349</v>
       </c>
       <c r="R23" t="n">
-        <v>6779955</v>
+        <v>6779557</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3062,7 +3063,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3072,7 +3073,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3081,7 +3082,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3317,7 +3317,7 @@
         <v>128837995</v>
       </c>
       <c r="B26" t="n">
-        <v>90552</v>
+        <v>90555</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3971,32 +3971,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128838013</v>
+        <v>128838043</v>
       </c>
       <c r="B32" t="n">
-        <v>79034</v>
+        <v>8450</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4006,10 +4006,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>496280</v>
+        <v>496351</v>
       </c>
       <c r="R32" t="n">
-        <v>6779962</v>
+        <v>6780109</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4041,7 +4041,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4051,7 +4051,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4078,32 +4078,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128838043</v>
+        <v>128838013</v>
       </c>
       <c r="B33" t="n">
-        <v>8450</v>
+        <v>79034</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4113,10 +4113,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>496351</v>
+        <v>496280</v>
       </c>
       <c r="R33" t="n">
-        <v>6780109</v>
+        <v>6779962</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4148,7 +4148,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4158,7 +4158,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD33" t="b">

--- a/artfynd/A 39682-2025 artfynd.xlsx
+++ b/artfynd/A 39682-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128838055</v>
       </c>
       <c r="B2" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>128838023</v>
       </c>
       <c r="B4" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
         <v>128838012</v>
       </c>
       <c r="B5" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
         <v>128838010</v>
       </c>
       <c r="B6" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         <v>128838047</v>
       </c>
       <c r="B9" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1567,32 +1567,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128838011</v>
+        <v>128838045</v>
       </c>
       <c r="B10" t="n">
-        <v>79034</v>
+        <v>43982</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>101735</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1602,10 +1602,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>496295</v>
+        <v>496345</v>
       </c>
       <c r="R10" t="n">
-        <v>6779954</v>
+        <v>6780049</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1656,6 +1656,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1674,32 +1675,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128838045</v>
+        <v>128838011</v>
       </c>
       <c r="B11" t="n">
-        <v>43982</v>
+        <v>79035</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>101735</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1709,10 +1710,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>496345</v>
+        <v>496295</v>
       </c>
       <c r="R11" t="n">
-        <v>6780049</v>
+        <v>6779954</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1744,7 +1745,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1754,7 +1755,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1763,7 +1764,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1785,7 +1785,7 @@
         <v>128838046</v>
       </c>
       <c r="B12" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         <v>128838048</v>
       </c>
       <c r="B13" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2008,7 +2008,7 @@
         <v>128838049</v>
       </c>
       <c r="B14" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2115,7 +2115,7 @@
         <v>128838009</v>
       </c>
       <c r="B15" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
         <v>128838050</v>
       </c>
       <c r="B16" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>128838017</v>
       </c>
       <c r="B17" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2442,48 +2442,48 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128842520</v>
+        <v>128838052</v>
       </c>
       <c r="B18" t="n">
-        <v>57723</v>
+        <v>92819</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Hästmyr, Hästmyr, Dlr</t>
+          <t>Hästmyr, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>496283</v>
+        <v>496237</v>
       </c>
       <c r="R18" t="n">
-        <v>6779932</v>
+        <v>6780285</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2522,12 +2522,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Bohål I Björk</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2536,66 +2531,67 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Jakob Bowers</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Jakob Bowers</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128838052</v>
+        <v>128842520</v>
       </c>
       <c r="B19" t="n">
-        <v>92816</v>
+        <v>57723</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Hästmyr, Dlr</t>
+          <t>Hästmyr, Hästmyr, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>496237</v>
+        <v>496283</v>
       </c>
       <c r="R19" t="n">
-        <v>6780285</v>
+        <v>6779932</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2624,7 +2620,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2634,7 +2630,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Bohål I Björk</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2643,19 +2644,18 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Jakob Bowers</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Jakob Bowers</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2665,7 +2665,7 @@
         <v>128838007</v>
       </c>
       <c r="B20" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2781,7 +2781,7 @@
         <v>128838020</v>
       </c>
       <c r="B21" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2885,32 +2885,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128837996</v>
+        <v>128838021</v>
       </c>
       <c r="B22" t="n">
-        <v>79653</v>
+        <v>92819</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2920,10 +2920,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>496236</v>
+        <v>496349</v>
       </c>
       <c r="R22" t="n">
-        <v>6779955</v>
+        <v>6779557</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2965,7 +2965,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2974,7 +2974,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2993,32 +2992,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128838021</v>
+        <v>128837996</v>
       </c>
       <c r="B23" t="n">
-        <v>92816</v>
+        <v>79654</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3028,10 +3027,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>496349</v>
+        <v>496236</v>
       </c>
       <c r="R23" t="n">
-        <v>6779557</v>
+        <v>6779955</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3063,7 +3062,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3073,7 +3072,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3082,6 +3081,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3210,7 +3210,7 @@
         <v>128838014</v>
       </c>
       <c r="B25" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3317,7 +3317,7 @@
         <v>128837995</v>
       </c>
       <c r="B26" t="n">
-        <v>90555</v>
+        <v>90558</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3425,7 +3425,7 @@
         <v>128837997</v>
       </c>
       <c r="B27" t="n">
-        <v>79653</v>
+        <v>79654</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3760,7 +3760,7 @@
         <v>128838019</v>
       </c>
       <c r="B30" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3867,7 +3867,7 @@
         <v>128838015</v>
       </c>
       <c r="B31" t="n">
-        <v>79034</v>
+        <v>79035</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3971,32 +3971,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128838043</v>
+        <v>128838013</v>
       </c>
       <c r="B32" t="n">
-        <v>8450</v>
+        <v>79035</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4006,10 +4006,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>496351</v>
+        <v>496280</v>
       </c>
       <c r="R32" t="n">
-        <v>6780109</v>
+        <v>6779962</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4041,7 +4041,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4051,7 +4051,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4078,32 +4078,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128838013</v>
+        <v>128838043</v>
       </c>
       <c r="B33" t="n">
-        <v>79034</v>
+        <v>8450</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4113,10 +4113,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>496280</v>
+        <v>496351</v>
       </c>
       <c r="R33" t="n">
-        <v>6779962</v>
+        <v>6780109</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4148,7 +4148,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4158,7 +4158,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD33" t="b">

--- a/artfynd/A 39682-2025 artfynd.xlsx
+++ b/artfynd/A 39682-2025 artfynd.xlsx
@@ -1567,32 +1567,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128838045</v>
+        <v>128838011</v>
       </c>
       <c r="B10" t="n">
-        <v>43982</v>
+        <v>79035</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>101735</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1602,10 +1602,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>496345</v>
+        <v>496295</v>
       </c>
       <c r="R10" t="n">
-        <v>6780049</v>
+        <v>6779954</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1656,7 +1656,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1675,32 +1674,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128838011</v>
+        <v>128838045</v>
       </c>
       <c r="B11" t="n">
-        <v>79035</v>
+        <v>43982</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>101735</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1710,10 +1709,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>496295</v>
+        <v>496345</v>
       </c>
       <c r="R11" t="n">
-        <v>6779954</v>
+        <v>6780049</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1745,7 +1744,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1755,7 +1754,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1764,6 +1763,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -3971,32 +3971,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128838013</v>
+        <v>128838043</v>
       </c>
       <c r="B32" t="n">
-        <v>79035</v>
+        <v>8450</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4006,10 +4006,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>496280</v>
+        <v>496351</v>
       </c>
       <c r="R32" t="n">
-        <v>6779962</v>
+        <v>6780109</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4041,7 +4041,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4051,7 +4051,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4078,32 +4078,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128838043</v>
+        <v>128838013</v>
       </c>
       <c r="B33" t="n">
-        <v>8450</v>
+        <v>79035</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4113,10 +4113,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>496351</v>
+        <v>496280</v>
       </c>
       <c r="R33" t="n">
-        <v>6780109</v>
+        <v>6779962</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4148,7 +4148,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4158,7 +4158,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD33" t="b">

--- a/artfynd/A 39682-2025 artfynd.xlsx
+++ b/artfynd/A 39682-2025 artfynd.xlsx
@@ -1116,48 +1116,45 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128838010</v>
+        <v>128838005</v>
       </c>
       <c r="B6" t="n">
-        <v>79035</v>
+        <v>43982</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>101735</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hästmyr, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>496332</v>
+        <v>496344</v>
       </c>
       <c r="R6" t="n">
-        <v>6779876</v>
+        <v>6779645</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1189,7 +1186,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1199,12 +1196,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:17</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1232,45 +1224,53 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128838005</v>
+        <v>128838001</v>
       </c>
       <c r="B7" t="n">
-        <v>43982</v>
+        <v>57723</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>101735</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hästmyr, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>496344</v>
+        <v>496347</v>
       </c>
       <c r="R7" t="n">
-        <v>6779645</v>
+        <v>6779846</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1302,7 +1302,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1312,7 +1312,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Ringhack högt upp på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1321,7 +1326,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1340,10 +1344,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128838001</v>
+        <v>128838010</v>
       </c>
       <c r="B8" t="n">
-        <v>57723</v>
+        <v>79035</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1351,31 +1355,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1383,10 +1382,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>496347</v>
+        <v>496332</v>
       </c>
       <c r="R8" t="n">
-        <v>6779846</v>
+        <v>6779876</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1418,7 +1417,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1428,12 +1427,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Ringhack högt upp på tall</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1442,6 +1441,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -2885,32 +2885,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128838021</v>
+        <v>128838041</v>
       </c>
       <c r="B22" t="n">
-        <v>92819</v>
+        <v>57720</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2920,10 +2920,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>496349</v>
+        <v>496237</v>
       </c>
       <c r="R22" t="n">
-        <v>6779557</v>
+        <v>6780345</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2965,7 +2965,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2992,32 +2992,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128837996</v>
+        <v>128838021</v>
       </c>
       <c r="B23" t="n">
-        <v>79654</v>
+        <v>92819</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3027,10 +3027,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>496236</v>
+        <v>496349</v>
       </c>
       <c r="R23" t="n">
-        <v>6779955</v>
+        <v>6779557</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3062,7 +3062,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3072,7 +3072,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3081,7 +3081,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3100,10 +3099,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128838041</v>
+        <v>128837996</v>
       </c>
       <c r="B24" t="n">
-        <v>57720</v>
+        <v>79654</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3111,21 +3110,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3135,10 +3134,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>496237</v>
+        <v>496236</v>
       </c>
       <c r="R24" t="n">
-        <v>6780345</v>
+        <v>6779955</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3170,7 +3169,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3180,7 +3179,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3189,6 +3188,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3971,32 +3971,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128838043</v>
+        <v>128838013</v>
       </c>
       <c r="B32" t="n">
-        <v>8450</v>
+        <v>79035</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4006,10 +4006,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>496351</v>
+        <v>496280</v>
       </c>
       <c r="R32" t="n">
-        <v>6780109</v>
+        <v>6779962</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4041,7 +4041,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4051,7 +4051,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4078,32 +4078,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128838013</v>
+        <v>128838043</v>
       </c>
       <c r="B33" t="n">
-        <v>79035</v>
+        <v>8450</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4113,10 +4113,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>496280</v>
+        <v>496351</v>
       </c>
       <c r="R33" t="n">
-        <v>6779962</v>
+        <v>6780109</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4148,7 +4148,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4158,7 +4158,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD33" t="b">

--- a/artfynd/A 39682-2025 artfynd.xlsx
+++ b/artfynd/A 39682-2025 artfynd.xlsx
@@ -675,45 +675,53 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128838055</v>
+        <v>128838036</v>
       </c>
       <c r="B2" t="n">
-        <v>92819</v>
+        <v>57723</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hästmyr, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>496351</v>
+        <v>496264</v>
       </c>
       <c r="R2" t="n">
-        <v>6780081</v>
+        <v>6780257</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +763,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack högt på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,53 +795,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128838036</v>
+        <v>128838055</v>
       </c>
       <c r="B3" t="n">
-        <v>57723</v>
+        <v>92819</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hästmyr, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>496264</v>
+        <v>496351</v>
       </c>
       <c r="R3" t="n">
-        <v>6780257</v>
+        <v>6780081</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,7 +865,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -870,12 +875,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:43</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack högt på tall</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -2662,7 +2662,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128838007</v>
+        <v>128838020</v>
       </c>
       <c r="B20" t="n">
         <v>79035</v>
@@ -2691,19 +2691,16 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hästmyr, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>496367</v>
+        <v>496336</v>
       </c>
       <c r="R20" t="n">
-        <v>6779675</v>
+        <v>6779865</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2735,7 +2732,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2745,12 +2742,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:35</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2759,7 +2751,6 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
-      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2778,7 +2769,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128838020</v>
+        <v>128838007</v>
       </c>
       <c r="B21" t="n">
         <v>79035</v>
@@ -2807,16 +2798,19 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Hästmyr, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>496336</v>
+        <v>496367</v>
       </c>
       <c r="R21" t="n">
-        <v>6779865</v>
+        <v>6779675</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2848,7 +2842,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2858,7 +2852,12 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2867,6 +2866,7 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2885,32 +2885,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128838041</v>
+        <v>128838021</v>
       </c>
       <c r="B22" t="n">
-        <v>57720</v>
+        <v>92819</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2920,10 +2920,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>496237</v>
+        <v>496349</v>
       </c>
       <c r="R22" t="n">
-        <v>6780345</v>
+        <v>6779557</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2965,7 +2965,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2992,32 +2992,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128838021</v>
+        <v>128837996</v>
       </c>
       <c r="B23" t="n">
-        <v>92819</v>
+        <v>79654</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3027,10 +3027,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>496349</v>
+        <v>496236</v>
       </c>
       <c r="R23" t="n">
-        <v>6779557</v>
+        <v>6779955</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3062,7 +3062,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3072,7 +3072,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3081,6 +3081,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3099,10 +3100,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128837996</v>
+        <v>128838041</v>
       </c>
       <c r="B24" t="n">
-        <v>79654</v>
+        <v>57720</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3110,21 +3111,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3134,10 +3135,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>496236</v>
+        <v>496237</v>
       </c>
       <c r="R24" t="n">
-        <v>6779955</v>
+        <v>6780345</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3169,7 +3170,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3179,7 +3180,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3188,7 +3189,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 39682-2025 artfynd.xlsx
+++ b/artfynd/A 39682-2025 artfynd.xlsx
@@ -675,53 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128838036</v>
+        <v>128838055</v>
       </c>
       <c r="B2" t="n">
-        <v>57723</v>
+        <v>92826</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hästmyr, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>496264</v>
+        <v>496351</v>
       </c>
       <c r="R2" t="n">
-        <v>6780257</v>
+        <v>6780081</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,12 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:43</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack högt på tall</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,45 +782,53 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128838055</v>
+        <v>128838036</v>
       </c>
       <c r="B3" t="n">
-        <v>92819</v>
+        <v>57725</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hästmyr, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>496351</v>
+        <v>496264</v>
       </c>
       <c r="R3" t="n">
-        <v>6780081</v>
+        <v>6780257</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -875,7 +870,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack högt på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,7 +905,7 @@
         <v>128838023</v>
       </c>
       <c r="B4" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
         <v>128838012</v>
       </c>
       <c r="B5" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1224,10 +1224,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128838001</v>
+        <v>128838010</v>
       </c>
       <c r="B7" t="n">
-        <v>57723</v>
+        <v>79039</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1235,31 +1235,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1267,10 +1262,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>496347</v>
+        <v>496332</v>
       </c>
       <c r="R7" t="n">
-        <v>6779846</v>
+        <v>6779876</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1302,7 +1297,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1312,12 +1307,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Ringhack högt upp på tall</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1326,6 +1321,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1344,10 +1340,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128838010</v>
+        <v>128838001</v>
       </c>
       <c r="B8" t="n">
-        <v>79035</v>
+        <v>57725</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1355,26 +1351,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
@@ -1382,10 +1383,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>496332</v>
+        <v>496347</v>
       </c>
       <c r="R8" t="n">
-        <v>6779876</v>
+        <v>6779846</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,7 +1418,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1427,12 +1428,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack högt upp på tall</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1441,7 +1442,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1463,7 +1463,7 @@
         <v>128838047</v>
       </c>
       <c r="B9" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         <v>128838011</v>
       </c>
       <c r="B10" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1782,10 +1782,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128838046</v>
+        <v>128838048</v>
       </c>
       <c r="B12" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1811,19 +1811,16 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hästmyr, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>496348</v>
+        <v>496271</v>
       </c>
       <c r="R12" t="n">
-        <v>6780084</v>
+        <v>6780378</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1855,7 +1852,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1865,12 +1862,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:51</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1879,7 +1871,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1898,10 +1889,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128838048</v>
+        <v>128838046</v>
       </c>
       <c r="B13" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1927,16 +1918,19 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hästmyr, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>496271</v>
+        <v>496348</v>
       </c>
       <c r="R13" t="n">
-        <v>6780378</v>
+        <v>6780084</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1968,7 +1962,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1978,7 +1972,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1987,6 +1986,7 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
+      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2005,10 +2005,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128838049</v>
+        <v>128838050</v>
       </c>
       <c r="B14" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2040,10 +2040,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>496350</v>
+        <v>496259</v>
       </c>
       <c r="R14" t="n">
-        <v>6780093</v>
+        <v>6780405</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2085,7 +2085,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2115,7 +2115,7 @@
         <v>128838009</v>
       </c>
       <c r="B15" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2228,10 +2228,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128838050</v>
+        <v>128838049</v>
       </c>
       <c r="B16" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2263,10 +2263,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>496259</v>
+        <v>496350</v>
       </c>
       <c r="R16" t="n">
-        <v>6780405</v>
+        <v>6780093</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2308,7 +2308,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2338,7 +2338,7 @@
         <v>128838017</v>
       </c>
       <c r="B17" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2442,48 +2442,48 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128838052</v>
+        <v>128842520</v>
       </c>
       <c r="B18" t="n">
-        <v>92819</v>
+        <v>57725</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Hästmyr, Dlr</t>
+          <t>Hästmyr, Hästmyr, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>496237</v>
+        <v>496283</v>
       </c>
       <c r="R18" t="n">
-        <v>6780285</v>
+        <v>6779932</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2522,7 +2522,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Bohål I Björk</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2531,67 +2536,66 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Jakob Bowers</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Jakob Bowers</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128842520</v>
+        <v>128838052</v>
       </c>
       <c r="B19" t="n">
-        <v>57723</v>
+        <v>92826</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Hästmyr, Hästmyr, Dlr</t>
+          <t>Hästmyr, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>496283</v>
+        <v>496237</v>
       </c>
       <c r="R19" t="n">
-        <v>6779932</v>
+        <v>6780285</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2620,7 +2624,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2630,12 +2634,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Bohål I Björk</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2644,18 +2643,19 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Jakob Bowers</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Jakob Bowers</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2665,7 +2665,7 @@
         <v>128838020</v>
       </c>
       <c r="B20" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2772,7 +2772,7 @@
         <v>128838007</v>
       </c>
       <c r="B21" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2885,32 +2885,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128838021</v>
+        <v>128837996</v>
       </c>
       <c r="B22" t="n">
-        <v>92819</v>
+        <v>79658</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2920,10 +2920,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>496349</v>
+        <v>496236</v>
       </c>
       <c r="R22" t="n">
-        <v>6779557</v>
+        <v>6779955</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2965,7 +2965,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2974,6 +2974,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2992,32 +2993,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128837996</v>
+        <v>128838021</v>
       </c>
       <c r="B23" t="n">
-        <v>79654</v>
+        <v>92826</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3027,10 +3028,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>496236</v>
+        <v>496349</v>
       </c>
       <c r="R23" t="n">
-        <v>6779955</v>
+        <v>6779557</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3062,7 +3063,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3072,7 +3073,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3081,7 +3082,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3103,7 +3103,7 @@
         <v>128838041</v>
       </c>
       <c r="B24" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3210,7 +3210,7 @@
         <v>128838014</v>
       </c>
       <c r="B25" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3317,7 +3317,7 @@
         <v>128837995</v>
       </c>
       <c r="B26" t="n">
-        <v>90558</v>
+        <v>90562</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3425,7 +3425,7 @@
         <v>128837997</v>
       </c>
       <c r="B27" t="n">
-        <v>79654</v>
+        <v>79658</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3533,7 +3533,7 @@
         <v>128838328</v>
       </c>
       <c r="B28" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3760,7 +3760,7 @@
         <v>128838019</v>
       </c>
       <c r="B30" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3867,7 +3867,7 @@
         <v>128838015</v>
       </c>
       <c r="B31" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3974,7 +3974,7 @@
         <v>128838013</v>
       </c>
       <c r="B32" t="n">
-        <v>79035</v>
+        <v>79039</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>

--- a/artfynd/A 39682-2025 artfynd.xlsx
+++ b/artfynd/A 39682-2025 artfynd.xlsx
@@ -1116,45 +1116,53 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128838005</v>
+        <v>128838001</v>
       </c>
       <c r="B6" t="n">
-        <v>43982</v>
+        <v>57725</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>101735</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hästmyr, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>496344</v>
+        <v>496347</v>
       </c>
       <c r="R6" t="n">
-        <v>6779645</v>
+        <v>6779846</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1186,7 +1194,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1196,7 +1204,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Ringhack högt upp på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1205,7 +1218,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1340,53 +1352,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128838001</v>
+        <v>128838005</v>
       </c>
       <c r="B8" t="n">
-        <v>57725</v>
+        <v>43982</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>100109</v>
+        <v>101735</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hästmyr, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>496347</v>
+        <v>496344</v>
       </c>
       <c r="R8" t="n">
-        <v>6779846</v>
+        <v>6779645</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1418,7 +1422,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1428,12 +1432,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:21</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Ringhack högt upp på tall</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1442,6 +1441,7 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
+      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -2442,48 +2442,48 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128842520</v>
+        <v>128838052</v>
       </c>
       <c r="B18" t="n">
-        <v>57725</v>
+        <v>92826</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Hästmyr, Hästmyr, Dlr</t>
+          <t>Hästmyr, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>496283</v>
+        <v>496237</v>
       </c>
       <c r="R18" t="n">
-        <v>6779932</v>
+        <v>6780285</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2522,12 +2522,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Bohål I Björk</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2536,66 +2531,67 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Jakob Bowers</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Jakob Bowers</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128838052</v>
+        <v>128842520</v>
       </c>
       <c r="B19" t="n">
-        <v>92826</v>
+        <v>57725</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Hästmyr, Dlr</t>
+          <t>Hästmyr, Hästmyr, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>496237</v>
+        <v>496283</v>
       </c>
       <c r="R19" t="n">
-        <v>6780285</v>
+        <v>6779932</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2624,7 +2620,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2634,7 +2630,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Bohål I Björk</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2643,19 +2644,18 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Jakob Bowers</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Jakob Bowers</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>

--- a/artfynd/A 39682-2025 artfynd.xlsx
+++ b/artfynd/A 39682-2025 artfynd.xlsx
@@ -675,45 +675,53 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128838055</v>
+        <v>128838036</v>
       </c>
       <c r="B2" t="n">
-        <v>92826</v>
+        <v>57725</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hästmyr, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>496351</v>
+        <v>496264</v>
       </c>
       <c r="R2" t="n">
-        <v>6780081</v>
+        <v>6780257</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +763,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack högt på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,53 +795,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128838036</v>
+        <v>128838055</v>
       </c>
       <c r="B3" t="n">
-        <v>57725</v>
+        <v>92833</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hästmyr, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>496264</v>
+        <v>496351</v>
       </c>
       <c r="R3" t="n">
-        <v>6780257</v>
+        <v>6780081</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,7 +865,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -870,12 +875,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:43</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack högt på tall</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,7 +905,7 @@
         <v>128838023</v>
       </c>
       <c r="B4" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1116,10 +1116,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128838001</v>
+        <v>128838010</v>
       </c>
       <c r="B6" t="n">
-        <v>57725</v>
+        <v>79039</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1127,31 +1127,26 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1159,10 +1154,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>496347</v>
+        <v>496332</v>
       </c>
       <c r="R6" t="n">
-        <v>6779846</v>
+        <v>6779876</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,7 +1189,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1204,12 +1199,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack högt upp på tall</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1218,6 +1213,7 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1236,10 +1232,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128838010</v>
+        <v>128838001</v>
       </c>
       <c r="B7" t="n">
-        <v>79039</v>
+        <v>57725</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1247,26 +1243,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
       <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1274,10 +1275,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>496332</v>
+        <v>496347</v>
       </c>
       <c r="R7" t="n">
-        <v>6779876</v>
+        <v>6779846</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1309,7 +1310,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1319,12 +1320,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack högt upp på tall</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1333,7 +1334,6 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1782,7 +1782,7 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128838048</v>
+        <v>128838046</v>
       </c>
       <c r="B12" t="n">
         <v>79039</v>
@@ -1811,16 +1811,19 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hästmyr, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>496271</v>
+        <v>496348</v>
       </c>
       <c r="R12" t="n">
-        <v>6780378</v>
+        <v>6780084</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1852,7 +1855,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1862,7 +1865,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>14:51</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1871,6 +1879,7 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1889,7 +1898,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128838046</v>
+        <v>128838048</v>
       </c>
       <c r="B13" t="n">
         <v>79039</v>
@@ -1918,19 +1927,16 @@
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Hästmyr, Dlr</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>496348</v>
+        <v>496271</v>
       </c>
       <c r="R13" t="n">
-        <v>6780084</v>
+        <v>6780378</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1962,7 +1968,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1972,12 +1978,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:51</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1986,7 +1987,6 @@
       <c r="AE13" t="b">
         <v>0</v>
       </c>
-      <c r="AF13" t="inlineStr"/>
       <c r="AG13" t="b">
         <v>0</v>
       </c>
@@ -2005,7 +2005,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128838050</v>
+        <v>128838049</v>
       </c>
       <c r="B14" t="n">
         <v>79039</v>
@@ -2040,10 +2040,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>496259</v>
+        <v>496350</v>
       </c>
       <c r="R14" t="n">
-        <v>6780405</v>
+        <v>6780093</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2085,7 +2085,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2228,7 +2228,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128838049</v>
+        <v>128838050</v>
       </c>
       <c r="B16" t="n">
         <v>79039</v>
@@ -2263,10 +2263,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>496350</v>
+        <v>496259</v>
       </c>
       <c r="R16" t="n">
-        <v>6780093</v>
+        <v>6780405</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2308,7 +2308,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2445,7 +2445,7 @@
         <v>128838052</v>
       </c>
       <c r="B18" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2662,7 +2662,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128838020</v>
+        <v>128838007</v>
       </c>
       <c r="B20" t="n">
         <v>79039</v>
@@ -2691,16 +2691,19 @@
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Hästmyr, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>496336</v>
+        <v>496367</v>
       </c>
       <c r="R20" t="n">
-        <v>6779865</v>
+        <v>6779675</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2732,7 +2735,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2742,7 +2745,12 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2751,6 +2759,7 @@
       <c r="AE20" t="b">
         <v>0</v>
       </c>
+      <c r="AF20" t="inlineStr"/>
       <c r="AG20" t="b">
         <v>0</v>
       </c>
@@ -2769,7 +2778,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128838007</v>
+        <v>128838020</v>
       </c>
       <c r="B21" t="n">
         <v>79039</v>
@@ -2798,19 +2807,16 @@
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
           <t>Hästmyr, Dlr</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>496367</v>
+        <v>496336</v>
       </c>
       <c r="R21" t="n">
-        <v>6779675</v>
+        <v>6779865</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2842,7 +2848,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2852,12 +2858,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:35</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2866,7 +2867,6 @@
       <c r="AE21" t="b">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2885,32 +2885,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128837996</v>
+        <v>128838021</v>
       </c>
       <c r="B22" t="n">
-        <v>79658</v>
+        <v>92833</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2920,10 +2920,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>496236</v>
+        <v>496349</v>
       </c>
       <c r="R22" t="n">
-        <v>6779955</v>
+        <v>6779557</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2965,7 +2965,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2974,7 +2974,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2993,32 +2992,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128838021</v>
+        <v>128837996</v>
       </c>
       <c r="B23" t="n">
-        <v>92826</v>
+        <v>79658</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3028,10 +3027,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>496349</v>
+        <v>496236</v>
       </c>
       <c r="R23" t="n">
-        <v>6779557</v>
+        <v>6779955</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3063,7 +3062,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3073,7 +3072,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3082,6 +3081,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3317,7 +3317,7 @@
         <v>128837995</v>
       </c>
       <c r="B26" t="n">
-        <v>90562</v>
+        <v>90569</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3971,32 +3971,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128838013</v>
+        <v>128838043</v>
       </c>
       <c r="B32" t="n">
-        <v>79039</v>
+        <v>8450</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4006,10 +4006,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>496280</v>
+        <v>496351</v>
       </c>
       <c r="R32" t="n">
-        <v>6779962</v>
+        <v>6780109</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4041,7 +4041,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4051,7 +4051,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4078,32 +4078,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128838043</v>
+        <v>128838013</v>
       </c>
       <c r="B33" t="n">
-        <v>8450</v>
+        <v>79039</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4113,10 +4113,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>496351</v>
+        <v>496280</v>
       </c>
       <c r="R33" t="n">
-        <v>6780109</v>
+        <v>6779962</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4148,7 +4148,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4158,7 +4158,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD33" t="b">

--- a/artfynd/A 39682-2025 artfynd.xlsx
+++ b/artfynd/A 39682-2025 artfynd.xlsx
@@ -675,53 +675,45 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128838036</v>
+        <v>128838055</v>
       </c>
       <c r="B2" t="n">
-        <v>57725</v>
+        <v>92835</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hästmyr, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>496264</v>
+        <v>496351</v>
       </c>
       <c r="R2" t="n">
-        <v>6780257</v>
+        <v>6780081</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,12 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:43</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack högt på tall</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -795,45 +782,53 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128838055</v>
+        <v>128838036</v>
       </c>
       <c r="B3" t="n">
-        <v>92833</v>
+        <v>57727</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hästmyr, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>496351</v>
+        <v>496264</v>
       </c>
       <c r="R3" t="n">
-        <v>6780081</v>
+        <v>6780257</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,7 +860,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -875,7 +870,12 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Ringhack högt på tall</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,7 +905,7 @@
         <v>128838023</v>
       </c>
       <c r="B4" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
         <v>128838012</v>
       </c>
       <c r="B5" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1119,7 +1119,7 @@
         <v>128838010</v>
       </c>
       <c r="B6" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1235,7 +1235,7 @@
         <v>128838001</v>
       </c>
       <c r="B7" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         <v>128838047</v>
       </c>
       <c r="B9" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1570,7 +1570,7 @@
         <v>128838011</v>
       </c>
       <c r="B10" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1785,7 +1785,7 @@
         <v>128838046</v>
       </c>
       <c r="B12" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         <v>128838048</v>
       </c>
       <c r="B13" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2008,7 +2008,7 @@
         <v>128838049</v>
       </c>
       <c r="B14" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2115,7 +2115,7 @@
         <v>128838009</v>
       </c>
       <c r="B15" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
         <v>128838050</v>
       </c>
       <c r="B16" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>128838017</v>
       </c>
       <c r="B17" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2442,48 +2442,48 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128838052</v>
+        <v>128842520</v>
       </c>
       <c r="B18" t="n">
-        <v>92833</v>
+        <v>57727</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Hästmyr, Dlr</t>
+          <t>Hästmyr, Hästmyr, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>496237</v>
+        <v>496283</v>
       </c>
       <c r="R18" t="n">
-        <v>6780285</v>
+        <v>6779932</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2522,7 +2522,12 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Bohål I Björk</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2531,67 +2536,66 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Jakob Bowers</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Jakob Bowers</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128842520</v>
+        <v>128838052</v>
       </c>
       <c r="B19" t="n">
-        <v>57725</v>
+        <v>92835</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Hästmyr, Hästmyr, Dlr</t>
+          <t>Hästmyr, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>496283</v>
+        <v>496237</v>
       </c>
       <c r="R19" t="n">
-        <v>6779932</v>
+        <v>6780285</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2620,7 +2624,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2630,12 +2634,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Bohål I Björk</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2644,18 +2643,19 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
+      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Jakob Bowers</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Jakob Bowers</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2665,7 +2665,7 @@
         <v>128838007</v>
       </c>
       <c r="B20" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2781,7 +2781,7 @@
         <v>128838020</v>
       </c>
       <c r="B21" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2885,32 +2885,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128838021</v>
+        <v>128837996</v>
       </c>
       <c r="B22" t="n">
-        <v>92833</v>
+        <v>79660</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2920,10 +2920,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>496349</v>
+        <v>496236</v>
       </c>
       <c r="R22" t="n">
-        <v>6779557</v>
+        <v>6779955</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2965,7 +2965,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2974,6 +2974,7 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2992,10 +2993,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128837996</v>
+        <v>128838041</v>
       </c>
       <c r="B23" t="n">
-        <v>79658</v>
+        <v>57724</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3003,21 +3004,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3027,10 +3028,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>496236</v>
+        <v>496237</v>
       </c>
       <c r="R23" t="n">
-        <v>6779955</v>
+        <v>6780345</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3062,7 +3063,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3072,7 +3073,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3081,7 +3082,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3100,32 +3100,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128838041</v>
+        <v>128838021</v>
       </c>
       <c r="B24" t="n">
-        <v>57722</v>
+        <v>92835</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3135,10 +3135,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>496237</v>
+        <v>496349</v>
       </c>
       <c r="R24" t="n">
-        <v>6780345</v>
+        <v>6779557</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3170,7 +3170,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3180,7 +3180,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3210,7 +3210,7 @@
         <v>128838014</v>
       </c>
       <c r="B25" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3317,7 +3317,7 @@
         <v>128837995</v>
       </c>
       <c r="B26" t="n">
-        <v>90569</v>
+        <v>90571</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3425,7 +3425,7 @@
         <v>128837997</v>
       </c>
       <c r="B27" t="n">
-        <v>79658</v>
+        <v>79660</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3533,7 +3533,7 @@
         <v>128838328</v>
       </c>
       <c r="B28" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3760,7 +3760,7 @@
         <v>128838019</v>
       </c>
       <c r="B30" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3867,7 +3867,7 @@
         <v>128838015</v>
       </c>
       <c r="B31" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4081,7 +4081,7 @@
         <v>128838013</v>
       </c>
       <c r="B33" t="n">
-        <v>79039</v>
+        <v>79041</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>

--- a/artfynd/A 39682-2025 artfynd.xlsx
+++ b/artfynd/A 39682-2025 artfynd.xlsx
@@ -1460,32 +1460,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128838047</v>
+        <v>128838045</v>
       </c>
       <c r="B9" t="n">
-        <v>79041</v>
+        <v>43982</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>101735</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1495,10 +1495,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>496281</v>
+        <v>496345</v>
       </c>
       <c r="R9" t="n">
-        <v>6780389</v>
+        <v>6780049</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1540,7 +1540,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1549,6 +1549,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1567,7 +1568,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128838011</v>
+        <v>128838047</v>
       </c>
       <c r="B10" t="n">
         <v>79041</v>
@@ -1602,10 +1603,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>496295</v>
+        <v>496281</v>
       </c>
       <c r="R10" t="n">
-        <v>6779954</v>
+        <v>6780389</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1637,7 +1638,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1647,7 +1648,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1674,32 +1675,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128838045</v>
+        <v>128838011</v>
       </c>
       <c r="B11" t="n">
-        <v>43982</v>
+        <v>79041</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>101735</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1709,10 +1710,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>496345</v>
+        <v>496295</v>
       </c>
       <c r="R11" t="n">
-        <v>6780049</v>
+        <v>6779954</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1744,7 +1745,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1754,7 +1755,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1763,7 +1764,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -2442,48 +2442,48 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128842520</v>
+        <v>128838052</v>
       </c>
       <c r="B18" t="n">
-        <v>57727</v>
+        <v>92835</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Hästmyr, Hästmyr, Dlr</t>
+          <t>Hästmyr, Dlr</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>496283</v>
+        <v>496237</v>
       </c>
       <c r="R18" t="n">
-        <v>6779932</v>
+        <v>6780285</v>
       </c>
       <c r="S18" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2512,7 +2512,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2522,12 +2522,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Bohål I Björk</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2536,66 +2531,67 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
+      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Jakob Bowers</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Jakob Bowers</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128838052</v>
+        <v>128842520</v>
       </c>
       <c r="B19" t="n">
-        <v>92835</v>
+        <v>57727</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Hästmyr, Dlr</t>
+          <t>Hästmyr, Hästmyr, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>496237</v>
+        <v>496283</v>
       </c>
       <c r="R19" t="n">
-        <v>6780285</v>
+        <v>6779932</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2624,7 +2620,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2634,7 +2630,12 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Bohål I Björk</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2643,19 +2644,18 @@
       <c r="AE19" t="b">
         <v>0</v>
       </c>
-      <c r="AF19" t="inlineStr"/>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Jakob Bowers</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Jakob Bowers</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2885,32 +2885,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128837996</v>
+        <v>128838021</v>
       </c>
       <c r="B22" t="n">
-        <v>79660</v>
+        <v>92835</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2920,10 +2920,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>496236</v>
+        <v>496349</v>
       </c>
       <c r="R22" t="n">
-        <v>6779955</v>
+        <v>6779557</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2965,7 +2965,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2974,7 +2974,6 @@
       <c r="AE22" t="b">
         <v>0</v>
       </c>
-      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -3100,32 +3099,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128838021</v>
+        <v>128837996</v>
       </c>
       <c r="B24" t="n">
-        <v>92835</v>
+        <v>79660</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3135,10 +3134,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>496349</v>
+        <v>496236</v>
       </c>
       <c r="R24" t="n">
-        <v>6779557</v>
+        <v>6779955</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3170,7 +3169,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3180,7 +3179,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3189,6 +3188,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3530,53 +3530,45 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128838328</v>
+        <v>128838042</v>
       </c>
       <c r="B28" t="n">
-        <v>57727</v>
+        <v>8450</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Hästmyr, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>496327</v>
+        <v>496270</v>
       </c>
       <c r="R28" t="n">
-        <v>6779866</v>
+        <v>6780214</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3608,7 +3600,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3618,12 +3610,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:05</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack högt på tall</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3650,45 +3637,53 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128838042</v>
+        <v>128838328</v>
       </c>
       <c r="B29" t="n">
-        <v>8450</v>
+        <v>57727</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Hästmyr, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>496270</v>
+        <v>496327</v>
       </c>
       <c r="R29" t="n">
-        <v>6780214</v>
+        <v>6779866</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3720,7 +3715,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3730,7 +3725,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack högt på tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3971,32 +3971,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128838043</v>
+        <v>128838013</v>
       </c>
       <c r="B32" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4006,10 +4006,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>496351</v>
+        <v>496280</v>
       </c>
       <c r="R32" t="n">
-        <v>6780109</v>
+        <v>6779962</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4041,7 +4041,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4051,7 +4051,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4078,32 +4078,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128838013</v>
+        <v>128838043</v>
       </c>
       <c r="B33" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4113,10 +4113,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>496280</v>
+        <v>496351</v>
       </c>
       <c r="R33" t="n">
-        <v>6779962</v>
+        <v>6780109</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4148,7 +4148,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4158,7 +4158,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD33" t="b">

--- a/artfynd/A 39682-2025 artfynd.xlsx
+++ b/artfynd/A 39682-2025 artfynd.xlsx
@@ -2885,32 +2885,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128838021</v>
+        <v>128838041</v>
       </c>
       <c r="B22" t="n">
-        <v>92835</v>
+        <v>57724</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2920,10 +2920,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>496349</v>
+        <v>496237</v>
       </c>
       <c r="R22" t="n">
-        <v>6779557</v>
+        <v>6780345</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2965,7 +2965,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2992,32 +2992,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128838041</v>
+        <v>128838021</v>
       </c>
       <c r="B23" t="n">
-        <v>57724</v>
+        <v>92835</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3027,10 +3027,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>496237</v>
+        <v>496349</v>
       </c>
       <c r="R23" t="n">
-        <v>6780345</v>
+        <v>6779557</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3062,7 +3062,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3072,7 +3072,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 39682-2025 artfynd.xlsx
+++ b/artfynd/A 39682-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128838055</v>
       </c>
       <c r="B2" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>128838023</v>
       </c>
       <c r="B4" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1460,32 +1460,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128838045</v>
+        <v>128838047</v>
       </c>
       <c r="B9" t="n">
-        <v>43982</v>
+        <v>79041</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>101735</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1495,10 +1495,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>496345</v>
+        <v>496281</v>
       </c>
       <c r="R9" t="n">
-        <v>6780049</v>
+        <v>6780389</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1540,7 +1540,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1549,7 +1549,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1568,7 +1567,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128838047</v>
+        <v>128838011</v>
       </c>
       <c r="B10" t="n">
         <v>79041</v>
@@ -1603,10 +1602,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>496281</v>
+        <v>496295</v>
       </c>
       <c r="R10" t="n">
-        <v>6780389</v>
+        <v>6779954</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1638,7 +1637,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1648,7 +1647,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1675,32 +1674,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128838011</v>
+        <v>128838045</v>
       </c>
       <c r="B11" t="n">
-        <v>79041</v>
+        <v>43982</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>101735</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1710,10 +1709,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>496295</v>
+        <v>496345</v>
       </c>
       <c r="R11" t="n">
-        <v>6779954</v>
+        <v>6780049</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1745,7 +1744,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1755,7 +1754,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1764,6 +1763,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -2445,7 +2445,7 @@
         <v>128838052</v>
       </c>
       <c r="B18" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2885,32 +2885,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128838041</v>
+        <v>128838021</v>
       </c>
       <c r="B22" t="n">
-        <v>57724</v>
+        <v>92821</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2920,10 +2920,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>496237</v>
+        <v>496349</v>
       </c>
       <c r="R22" t="n">
-        <v>6780345</v>
+        <v>6779557</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2965,7 +2965,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2992,32 +2992,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128838021</v>
+        <v>128837996</v>
       </c>
       <c r="B23" t="n">
-        <v>92835</v>
+        <v>79660</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3027,10 +3027,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>496349</v>
+        <v>496236</v>
       </c>
       <c r="R23" t="n">
-        <v>6779557</v>
+        <v>6779955</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3062,7 +3062,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3072,7 +3072,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3081,6 +3081,7 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3099,10 +3100,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128837996</v>
+        <v>128838041</v>
       </c>
       <c r="B24" t="n">
-        <v>79660</v>
+        <v>57724</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3110,21 +3111,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3134,10 +3135,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>496236</v>
+        <v>496237</v>
       </c>
       <c r="R24" t="n">
-        <v>6779955</v>
+        <v>6780345</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3169,7 +3170,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3179,7 +3180,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3188,7 +3189,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3317,7 +3317,7 @@
         <v>128837995</v>
       </c>
       <c r="B26" t="n">
-        <v>90571</v>
+        <v>90572</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3971,32 +3971,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128838013</v>
+        <v>128838043</v>
       </c>
       <c r="B32" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4006,10 +4006,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>496280</v>
+        <v>496351</v>
       </c>
       <c r="R32" t="n">
-        <v>6779962</v>
+        <v>6780109</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4041,7 +4041,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4051,7 +4051,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4078,32 +4078,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128838043</v>
+        <v>128838013</v>
       </c>
       <c r="B33" t="n">
-        <v>8450</v>
+        <v>79041</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4113,10 +4113,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>496351</v>
+        <v>496280</v>
       </c>
       <c r="R33" t="n">
-        <v>6780109</v>
+        <v>6779962</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4148,7 +4148,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4158,7 +4158,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD33" t="b">

--- a/artfynd/A 39682-2025 artfynd.xlsx
+++ b/artfynd/A 39682-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128838055</v>
       </c>
       <c r="B2" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -905,7 +905,7 @@
         <v>128838023</v>
       </c>
       <c r="B4" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1460,32 +1460,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128838047</v>
+        <v>128838045</v>
       </c>
       <c r="B9" t="n">
-        <v>79041</v>
+        <v>43982</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>101735</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1495,10 +1495,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>496281</v>
+        <v>496345</v>
       </c>
       <c r="R9" t="n">
-        <v>6780389</v>
+        <v>6780049</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1540,7 +1540,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1549,6 +1549,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1567,7 +1568,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128838011</v>
+        <v>128838047</v>
       </c>
       <c r="B10" t="n">
         <v>79041</v>
@@ -1602,10 +1603,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>496295</v>
+        <v>496281</v>
       </c>
       <c r="R10" t="n">
-        <v>6779954</v>
+        <v>6780389</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1637,7 +1638,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1647,7 +1648,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1674,32 +1675,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128838045</v>
+        <v>128838011</v>
       </c>
       <c r="B11" t="n">
-        <v>43982</v>
+        <v>79041</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>101735</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1709,10 +1710,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>496345</v>
+        <v>496295</v>
       </c>
       <c r="R11" t="n">
-        <v>6780049</v>
+        <v>6779954</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1744,7 +1745,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1754,7 +1755,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1763,7 +1764,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -2445,7 +2445,7 @@
         <v>128838052</v>
       </c>
       <c r="B18" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2888,7 +2888,7 @@
         <v>128838021</v>
       </c>
       <c r="B22" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2992,10 +2992,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128837996</v>
+        <v>128838041</v>
       </c>
       <c r="B23" t="n">
-        <v>79660</v>
+        <v>57724</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3003,21 +3003,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3027,10 +3027,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>496236</v>
+        <v>496237</v>
       </c>
       <c r="R23" t="n">
-        <v>6779955</v>
+        <v>6780345</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3062,7 +3062,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3072,7 +3072,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3081,7 +3081,6 @@
       <c r="AE23" t="b">
         <v>0</v>
       </c>
-      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3100,10 +3099,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128838041</v>
+        <v>128837996</v>
       </c>
       <c r="B24" t="n">
-        <v>57724</v>
+        <v>79660</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3111,21 +3110,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3135,10 +3134,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>496237</v>
+        <v>496236</v>
       </c>
       <c r="R24" t="n">
-        <v>6780345</v>
+        <v>6779955</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3170,7 +3169,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3180,7 +3179,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3189,6 +3188,7 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 39682-2025 artfynd.xlsx
+++ b/artfynd/A 39682-2025 artfynd.xlsx
@@ -1116,10 +1116,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128838010</v>
+        <v>128838001</v>
       </c>
       <c r="B6" t="n">
-        <v>79041</v>
+        <v>57727</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1127,26 +1127,31 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1154,10 +1159,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>496332</v>
+        <v>496347</v>
       </c>
       <c r="R6" t="n">
-        <v>6779876</v>
+        <v>6779846</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1189,7 +1194,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1199,12 +1204,12 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack högt upp på tall</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1213,7 +1218,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1232,53 +1236,45 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128838001</v>
+        <v>128838005</v>
       </c>
       <c r="B7" t="n">
-        <v>57727</v>
+        <v>43982</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>101735</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hästmyr, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>496347</v>
+        <v>496344</v>
       </c>
       <c r="R7" t="n">
-        <v>6779846</v>
+        <v>6779645</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1310,7 +1306,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1320,12 +1316,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:21</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Ringhack högt upp på tall</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1334,6 +1325,7 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
@@ -1352,45 +1344,48 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128838005</v>
+        <v>128838010</v>
       </c>
       <c r="B8" t="n">
-        <v>43982</v>
+        <v>79041</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>101735</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Hästmyr, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>496344</v>
+        <v>496332</v>
       </c>
       <c r="R8" t="n">
-        <v>6779645</v>
+        <v>6779876</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1422,7 +1417,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1432,7 +1427,12 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1460,32 +1460,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128838045</v>
+        <v>128838047</v>
       </c>
       <c r="B9" t="n">
-        <v>43982</v>
+        <v>79041</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>101735</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1495,10 +1495,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>496345</v>
+        <v>496281</v>
       </c>
       <c r="R9" t="n">
-        <v>6780049</v>
+        <v>6780389</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1530,7 +1530,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1540,7 +1540,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1549,7 +1549,6 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
-      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1568,32 +1567,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128838047</v>
+        <v>128838045</v>
       </c>
       <c r="B10" t="n">
-        <v>79041</v>
+        <v>43982</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>101735</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1603,10 +1602,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>496281</v>
+        <v>496345</v>
       </c>
       <c r="R10" t="n">
-        <v>6780389</v>
+        <v>6780049</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1638,7 +1637,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1648,7 +1647,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1657,6 +1656,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 39682-2025 artfynd.xlsx
+++ b/artfynd/A 39682-2025 artfynd.xlsx
@@ -675,45 +675,53 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128838055</v>
+        <v>128838036</v>
       </c>
       <c r="B2" t="n">
-        <v>92822</v>
+        <v>57727</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hästmyr, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>496351</v>
+        <v>496264</v>
       </c>
       <c r="R2" t="n">
-        <v>6780081</v>
+        <v>6780257</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -745,7 +753,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -755,7 +763,12 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Ringhack högt på tall</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -782,53 +795,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128838036</v>
+        <v>128838055</v>
       </c>
       <c r="B3" t="n">
-        <v>57727</v>
+        <v>92825</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Hästmyr, Dlr</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>496264</v>
+        <v>496351</v>
       </c>
       <c r="R3" t="n">
-        <v>6780257</v>
+        <v>6780081</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,7 +865,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -870,12 +875,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:43</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Ringhack högt på tall</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,7 +905,7 @@
         <v>128838023</v>
       </c>
       <c r="B4" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1012,7 +1012,7 @@
         <v>128838012</v>
       </c>
       <c r="B5" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1347,7 +1347,7 @@
         <v>128838010</v>
       </c>
       <c r="B8" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1463,7 +1463,7 @@
         <v>128838047</v>
       </c>
       <c r="B9" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1567,32 +1567,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128838045</v>
+        <v>128838011</v>
       </c>
       <c r="B10" t="n">
-        <v>43982</v>
+        <v>79043</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>101735</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1602,10 +1602,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>496345</v>
+        <v>496295</v>
       </c>
       <c r="R10" t="n">
-        <v>6780049</v>
+        <v>6779954</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1637,7 +1637,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1647,7 +1647,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1656,7 +1656,6 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
-      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1675,32 +1674,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128838011</v>
+        <v>128838045</v>
       </c>
       <c r="B11" t="n">
-        <v>79041</v>
+        <v>43982</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>101735</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1710,10 +1709,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>496295</v>
+        <v>496345</v>
       </c>
       <c r="R11" t="n">
-        <v>6779954</v>
+        <v>6780049</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1745,7 +1744,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1755,7 +1754,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>14:59</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1764,6 +1763,7 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1785,7 +1785,7 @@
         <v>128838046</v>
       </c>
       <c r="B12" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1901,7 +1901,7 @@
         <v>128838048</v>
       </c>
       <c r="B13" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2008,7 +2008,7 @@
         <v>128838049</v>
       </c>
       <c r="B14" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2115,7 +2115,7 @@
         <v>128838009</v>
       </c>
       <c r="B15" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2231,7 +2231,7 @@
         <v>128838050</v>
       </c>
       <c r="B16" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2338,7 +2338,7 @@
         <v>128838017</v>
       </c>
       <c r="B17" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
         <v>128838052</v>
       </c>
       <c r="B18" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2665,7 +2665,7 @@
         <v>128838007</v>
       </c>
       <c r="B20" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2781,7 +2781,7 @@
         <v>128838020</v>
       </c>
       <c r="B21" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2888,7 +2888,7 @@
         <v>128838021</v>
       </c>
       <c r="B22" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3102,7 +3102,7 @@
         <v>128837996</v>
       </c>
       <c r="B24" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3210,7 +3210,7 @@
         <v>128838014</v>
       </c>
       <c r="B25" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3317,7 +3317,7 @@
         <v>128837995</v>
       </c>
       <c r="B26" t="n">
-        <v>90572</v>
+        <v>90575</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3425,7 +3425,7 @@
         <v>128837997</v>
       </c>
       <c r="B27" t="n">
-        <v>79660</v>
+        <v>79662</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3530,45 +3530,53 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128838042</v>
+        <v>128838328</v>
       </c>
       <c r="B28" t="n">
-        <v>8450</v>
+        <v>57727</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Hästmyr, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>496270</v>
+        <v>496327</v>
       </c>
       <c r="R28" t="n">
-        <v>6780214</v>
+        <v>6779866</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3600,7 +3608,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3610,7 +3618,12 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Ringhack högt på tall</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3637,53 +3650,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128838328</v>
+        <v>128838042</v>
       </c>
       <c r="B29" t="n">
-        <v>57727</v>
+        <v>8450</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>106545</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Hästmyr, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>496327</v>
+        <v>496270</v>
       </c>
       <c r="R29" t="n">
-        <v>6779866</v>
+        <v>6780214</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3715,7 +3720,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3725,12 +3730,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>14:05</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack högt på tall</t>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3760,7 +3760,7 @@
         <v>128838019</v>
       </c>
       <c r="B30" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3867,7 +3867,7 @@
         <v>128838015</v>
       </c>
       <c r="B31" t="n">
-        <v>79041</v>
+        <v>79043</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3971,32 +3971,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128838043</v>
+        <v>128838013</v>
       </c>
       <c r="B32" t="n">
-        <v>8450</v>
+        <v>79043</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>106545</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -4006,10 +4006,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>496351</v>
+        <v>496280</v>
       </c>
       <c r="R32" t="n">
-        <v>6780109</v>
+        <v>6779962</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4041,7 +4041,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4051,7 +4051,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4078,32 +4078,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128838013</v>
+        <v>128838043</v>
       </c>
       <c r="B33" t="n">
-        <v>79041</v>
+        <v>8450</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>106545</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4113,10 +4113,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>496280</v>
+        <v>496351</v>
       </c>
       <c r="R33" t="n">
-        <v>6779962</v>
+        <v>6780109</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4148,7 +4148,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4158,7 +4158,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>14:49</t>
         </is>
       </c>
       <c r="AD33" t="b">

--- a/artfynd/A 39682-2025 artfynd.xlsx
+++ b/artfynd/A 39682-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY33"/>
+  <dimension ref="A1:AY36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128838036</v>
+        <v>128837995</v>
       </c>
       <c r="B2" t="n">
-        <v>57727</v>
+        <v>90932</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -686,42 +686,34 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100109</v>
+        <v>1962</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
           <t>Hästmyr, Dlr</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>496264</v>
+        <v>496293</v>
       </c>
       <c r="R2" t="n">
-        <v>6780257</v>
+        <v>6779895</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -753,7 +745,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -763,12 +755,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>14:43</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>Ringhack högt på tall</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -777,6 +764,7 @@
       <c r="AE2" t="b">
         <v>0</v>
       </c>
+      <c r="AF2" t="inlineStr"/>
       <c r="AG2" t="b">
         <v>0</v>
       </c>
@@ -795,14 +783,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128838055</v>
+        <v>128838021</v>
       </c>
       <c r="B3" t="n">
-        <v>92825</v>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -830,10 +818,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>496351</v>
+        <v>496349</v>
       </c>
       <c r="R3" t="n">
-        <v>6780081</v>
+        <v>6779557</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -865,7 +853,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -875,7 +863,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>14:52</t>
+          <t>16:11</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,11 +893,11 @@
         <v>128838023</v>
       </c>
       <c r="B4" t="n">
-        <v>92825</v>
+        <v>93197</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -1009,10 +997,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128838012</v>
+        <v>128838052</v>
       </c>
       <c r="B5" t="n">
-        <v>79043</v>
+        <v>93197</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1020,21 +1008,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1044,10 +1032,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>496288</v>
+        <v>496237</v>
       </c>
       <c r="R5" t="n">
-        <v>6779959</v>
+        <v>6780285</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1079,7 +1067,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1089,7 +1077,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>17:07</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1098,6 +1086,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1116,10 +1105,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128838001</v>
+        <v>128838055</v>
       </c>
       <c r="B6" t="n">
-        <v>57727</v>
+        <v>93197</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1127,42 +1116,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
           <t>Hästmyr, Dlr</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>496347</v>
+        <v>496351</v>
       </c>
       <c r="R6" t="n">
-        <v>6779846</v>
+        <v>6780081</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1194,7 +1175,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:21</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1204,12 +1185,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:21</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Ringhack högt upp på tall</t>
+          <t>14:52</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1236,45 +1212,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128838005</v>
+        <v>128838007</v>
       </c>
       <c r="B7" t="n">
-        <v>43982</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>101735</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Hästmyr, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>496344</v>
+        <v>496367</v>
       </c>
       <c r="R7" t="n">
-        <v>6779645</v>
+        <v>6779675</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1306,7 +1285,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:35</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1316,7 +1295,12 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>16:15</t>
+          <t>15:35</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1344,14 +1328,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128838010</v>
+        <v>128838008</v>
       </c>
       <c r="B8" t="n">
-        <v>79043</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1382,10 +1366,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>496332</v>
+        <v>496381</v>
       </c>
       <c r="R8" t="n">
-        <v>6779876</v>
+        <v>6779778</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,7 +1401,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1427,7 +1411,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>15:17</t>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
@@ -1460,14 +1444,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128838047</v>
+        <v>128838009</v>
       </c>
       <c r="B9" t="n">
-        <v>79043</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1489,16 +1473,19 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Hästmyr, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>496281</v>
+        <v>496340</v>
       </c>
       <c r="R9" t="n">
-        <v>6780389</v>
+        <v>6779846</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1530,7 +1517,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>15:23</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1540,7 +1527,12 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>15:23</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1549,6 +1541,7 @@
       <c r="AE9" t="b">
         <v>0</v>
       </c>
+      <c r="AF9" t="inlineStr"/>
       <c r="AG9" t="b">
         <v>0</v>
       </c>
@@ -1567,14 +1560,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128838011</v>
+        <v>128838010</v>
       </c>
       <c r="B10" t="n">
-        <v>79043</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1596,16 +1589,19 @@
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
           <t>Hästmyr, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>496295</v>
+        <v>496332</v>
       </c>
       <c r="R10" t="n">
-        <v>6779954</v>
+        <v>6779876</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1637,7 +1633,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1647,7 +1643,12 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>16:36</t>
+          <t>15:17</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1656,6 +1657,7 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
@@ -1674,32 +1676,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128838045</v>
+        <v>128838011</v>
       </c>
       <c r="B11" t="n">
-        <v>43982</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>101735</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1709,10 +1711,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>496345</v>
+        <v>496295</v>
       </c>
       <c r="R11" t="n">
-        <v>6780049</v>
+        <v>6779954</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1744,7 +1746,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1754,7 +1756,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:59</t>
+          <t>16:36</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1763,7 +1765,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1782,14 +1783,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128838046</v>
+        <v>128838012</v>
       </c>
       <c r="B12" t="n">
-        <v>79043</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1811,19 +1812,16 @@
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
           <t>Hästmyr, Dlr</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>496348</v>
+        <v>496288</v>
       </c>
       <c r="R12" t="n">
-        <v>6780084</v>
+        <v>6779959</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1855,7 +1853,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:51</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1865,12 +1863,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:51</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1879,7 +1872,6 @@
       <c r="AE12" t="b">
         <v>0</v>
       </c>
-      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
@@ -1898,14 +1890,14 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128838048</v>
+        <v>128838013</v>
       </c>
       <c r="B13" t="n">
-        <v>79043</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1933,10 +1925,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>496271</v>
+        <v>496280</v>
       </c>
       <c r="R13" t="n">
-        <v>6780378</v>
+        <v>6779962</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1968,7 +1960,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1978,7 +1970,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>17:20</t>
+          <t>16:34</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2005,14 +1997,14 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128838049</v>
+        <v>128838014</v>
       </c>
       <c r="B14" t="n">
-        <v>79043</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -2040,10 +2032,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>496350</v>
+        <v>496306</v>
       </c>
       <c r="R14" t="n">
-        <v>6780093</v>
+        <v>6779793</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2075,7 +2067,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2085,7 +2077,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:50</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2112,14 +2104,14 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128838009</v>
+        <v>128838015</v>
       </c>
       <c r="B15" t="n">
-        <v>79043</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2141,19 +2133,16 @@
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
           <t>Hästmyr, Dlr</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>496340</v>
+        <v>496343</v>
       </c>
       <c r="R15" t="n">
-        <v>6779846</v>
+        <v>6779566</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2185,7 +2174,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:23</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2195,12 +2184,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:23</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>16:12</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2209,7 +2193,6 @@
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2228,14 +2211,14 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128838050</v>
+        <v>128838017</v>
       </c>
       <c r="B16" t="n">
-        <v>79043</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2263,10 +2246,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>496259</v>
+        <v>496373</v>
       </c>
       <c r="R16" t="n">
-        <v>6780405</v>
+        <v>6779679</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2298,7 +2281,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2308,7 +2291,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:32</t>
+          <t>15:37</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2335,14 +2318,14 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128838017</v>
+        <v>128838018</v>
       </c>
       <c r="B17" t="n">
-        <v>79043</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2370,10 +2353,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>496373</v>
+        <v>496390</v>
       </c>
       <c r="R17" t="n">
-        <v>6779679</v>
+        <v>6779820</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2405,7 +2388,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2415,7 +2398,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>15:37</t>
+          <t>15:28</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2442,32 +2425,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128838052</v>
+        <v>128838019</v>
       </c>
       <c r="B18" t="n">
-        <v>92825</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2477,10 +2460,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>496237</v>
+        <v>496340</v>
       </c>
       <c r="R18" t="n">
-        <v>6780285</v>
+        <v>6779850</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2512,7 +2495,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2522,7 +2505,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>17:07</t>
+          <t>15:22</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2531,7 +2514,6 @@
       <c r="AE18" t="b">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr"/>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2550,48 +2532,48 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128842520</v>
+        <v>128838020</v>
       </c>
       <c r="B19" t="n">
-        <v>57727</v>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Hästmyr, Hästmyr, Dlr</t>
+          <t>Hästmyr, Dlr</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>496283</v>
+        <v>496336</v>
       </c>
       <c r="R19" t="n">
-        <v>6779932</v>
+        <v>6779865</v>
       </c>
       <c r="S19" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2620,7 +2602,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>16:00</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2630,12 +2612,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>16:00</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Bohål I Björk</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2650,26 +2627,26 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Jakob Bowers</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>FREDRIK Månsson</t>
+          <t>Jakob Bowers</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128838007</v>
+        <v>128838046</v>
       </c>
       <c r="B20" t="n">
-        <v>79043</v>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -2700,10 +2677,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>496367</v>
+        <v>496348</v>
       </c>
       <c r="R20" t="n">
-        <v>6779675</v>
+        <v>6780084</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2735,7 +2712,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2745,7 +2722,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>15:35</t>
+          <t>14:51</t>
         </is>
       </c>
       <c r="AC20" t="inlineStr">
@@ -2778,14 +2755,14 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128838020</v>
+        <v>128838047</v>
       </c>
       <c r="B21" t="n">
-        <v>79043</v>
+        <v>79327</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
@@ -2813,10 +2790,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>496336</v>
+        <v>496281</v>
       </c>
       <c r="R21" t="n">
-        <v>6779865</v>
+        <v>6780389</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2848,7 +2825,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2858,7 +2835,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2885,32 +2862,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128838021</v>
+        <v>128838048</v>
       </c>
       <c r="B22" t="n">
-        <v>92825</v>
+        <v>79327</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2920,10 +2897,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>496349</v>
+        <v>496271</v>
       </c>
       <c r="R22" t="n">
-        <v>6779557</v>
+        <v>6780378</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2955,7 +2932,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -2965,7 +2942,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>16:11</t>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2992,32 +2969,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128838041</v>
+        <v>128838049</v>
       </c>
       <c r="B23" t="n">
-        <v>57724</v>
+        <v>79327</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3027,10 +3004,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>496237</v>
+        <v>496350</v>
       </c>
       <c r="R23" t="n">
-        <v>6780345</v>
+        <v>6780093</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3062,7 +3039,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3072,7 +3049,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>17:13</t>
+          <t>14:50</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3099,32 +3076,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128837996</v>
+        <v>128838050</v>
       </c>
       <c r="B24" t="n">
-        <v>79662</v>
+        <v>79327</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3134,10 +3111,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>496236</v>
+        <v>496259</v>
       </c>
       <c r="R24" t="n">
-        <v>6779955</v>
+        <v>6780405</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3169,7 +3146,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3179,7 +3156,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>16:31</t>
+          <t>14:32</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3188,7 +3165,6 @@
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3207,10 +3183,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128838014</v>
+        <v>128837996</v>
       </c>
       <c r="B25" t="n">
-        <v>79043</v>
+        <v>79946</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3218,21 +3194,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3242,10 +3218,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>496306</v>
+        <v>496236</v>
       </c>
       <c r="R25" t="n">
-        <v>6779793</v>
+        <v>6779955</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3277,7 +3253,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3287,7 +3263,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:31</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3296,6 +3272,7 @@
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3314,10 +3291,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128837995</v>
+        <v>128837997</v>
       </c>
       <c r="B26" t="n">
-        <v>90575</v>
+        <v>79946</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3325,21 +3302,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1962</v>
+        <v>6453</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3349,10 +3326,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>496293</v>
+        <v>496278</v>
       </c>
       <c r="R26" t="n">
-        <v>6779895</v>
+        <v>6779883</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3384,7 +3361,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3394,7 +3371,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>16:27</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3422,32 +3399,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128837997</v>
+        <v>128838006</v>
       </c>
       <c r="B27" t="n">
-        <v>79662</v>
+        <v>57950</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6453</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3457,10 +3434,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>496278</v>
+        <v>496318</v>
       </c>
       <c r="R27" t="n">
-        <v>6779883</v>
+        <v>6779932</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3492,7 +3469,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3502,7 +3479,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>16:27</t>
+          <t>16:46</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3511,7 +3488,6 @@
       <c r="AE27" t="b">
         <v>0</v>
       </c>
-      <c r="AF27" t="inlineStr"/>
       <c r="AG27" t="b">
         <v>0</v>
       </c>
@@ -3530,27 +3506,27 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128838328</v>
+        <v>128838041</v>
       </c>
       <c r="B28" t="n">
-        <v>57727</v>
+        <v>57950</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>100049</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3559,24 +3535,16 @@
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Hästmyr, Dlr</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>496327</v>
+        <v>496237</v>
       </c>
       <c r="R28" t="n">
-        <v>6779866</v>
+        <v>6780345</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3608,7 +3576,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>14:05</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3618,12 +3586,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>14:05</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Ringhack högt på tall</t>
+          <t>17:13</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3650,45 +3613,53 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128838042</v>
+        <v>128838001</v>
       </c>
       <c r="B29" t="n">
-        <v>8450</v>
+        <v>57953</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>106545</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Hästmyr, Dlr</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>496270</v>
+        <v>496347</v>
       </c>
       <c r="R29" t="n">
-        <v>6780214</v>
+        <v>6779846</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3720,7 +3691,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>15:21</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3730,7 +3701,12 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>15:21</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack högt upp på tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3757,10 +3733,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128838019</v>
+        <v>128838036</v>
       </c>
       <c r="B30" t="n">
-        <v>79043</v>
+        <v>57953</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3768,34 +3744,42 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Hästmyr, Dlr</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>496340</v>
+        <v>496264</v>
       </c>
       <c r="R30" t="n">
-        <v>6779850</v>
+        <v>6780257</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3827,7 +3811,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3837,7 +3821,12 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>15:22</t>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Ringhack högt på tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3864,10 +3853,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128838015</v>
+        <v>128838328</v>
       </c>
       <c r="B31" t="n">
-        <v>79043</v>
+        <v>57953</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3875,34 +3864,42 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Hästmyr, Dlr</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>496343</v>
+        <v>496327</v>
       </c>
       <c r="R31" t="n">
-        <v>6779566</v>
+        <v>6779866</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3934,7 +3931,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -3944,7 +3941,12 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>16:12</t>
+          <t>14:05</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack högt på tall</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3971,10 +3973,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128838013</v>
+        <v>128842520</v>
       </c>
       <c r="B32" t="n">
-        <v>79043</v>
+        <v>57953</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3982,37 +3984,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Hästmyr, Dlr</t>
+          <t>Hästmyr, Hästmyr, Dlr</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>496280</v>
+        <v>496283</v>
       </c>
       <c r="R32" t="n">
-        <v>6779962</v>
+        <v>6779932</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4041,7 +4043,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4051,7 +4053,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>16:34</t>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Bohål I Björk</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4066,22 +4073,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Jakob Bowers</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Jakob Bowers</t>
+          <t>FREDRIK Månsson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128838043</v>
+        <v>128838005</v>
       </c>
       <c r="B33" t="n">
-        <v>8450</v>
+        <v>44177</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4089,21 +4096,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>106545</v>
+        <v>101735</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4113,10 +4120,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>496351</v>
+        <v>496344</v>
       </c>
       <c r="R33" t="n">
-        <v>6780109</v>
+        <v>6779645</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4148,7 +4155,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4158,7 +4165,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>14:49</t>
+          <t>16:15</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4167,6 +4174,7 @@
       <c r="AE33" t="b">
         <v>0</v>
       </c>
+      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
@@ -4182,6 +4190,328 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>128838045</v>
+      </c>
+      <c r="B34" t="n">
+        <v>44177</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>101735</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Jättesvampmal</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Scardia boletella</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Fabricius, 1794)</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Hästmyr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>496345</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6780049</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>14:59</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Jakob Bowers</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Jakob Bowers</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>128838042</v>
+      </c>
+      <c r="B35" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Hästmyr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>496270</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6780214</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="Z35" t="inlineStr">
+        <is>
+          <t>17:03</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB35" t="inlineStr">
+        <is>
+          <t>17:03</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Jakob Bowers</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Jakob Bowers</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>128838043</v>
+      </c>
+      <c r="B36" t="n">
+        <v>8455</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Hästmyr, Dlr</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>496351</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6780109</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Orsa</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-10-01</t>
+        </is>
+      </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>14:49</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Jakob Bowers</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Jakob Bowers</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 39682-2025 artfynd.xlsx
+++ b/artfynd/A 39682-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY36"/>
+  <dimension ref="A1:AZ36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -780,6 +785,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128837995</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -887,6 +897,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128838021</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -994,6 +1009,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128838023</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1102,6 +1122,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128838052</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1209,6 +1234,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128838055</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1325,6 +1355,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128838007</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1441,6 +1476,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128838008</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1557,6 +1597,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128838009</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1673,6 +1718,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128838010</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1780,6 +1830,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128838011</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1887,6 +1942,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128838012</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1994,6 +2054,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128838013</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2101,6 +2166,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128838014</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2208,6 +2278,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128838015</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2315,6 +2390,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128838017</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2422,6 +2502,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128838018</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2529,6 +2614,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128838019</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2636,6 +2726,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128838020</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2752,6 +2847,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128838046</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2859,6 +2959,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128838047</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2966,6 +3071,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128838048</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3073,6 +3183,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128838049</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3180,6 +3295,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128838050</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3288,6 +3408,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128837996</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3396,6 +3521,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128837997</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3503,6 +3633,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128838006</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3610,6 +3745,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128838041</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3730,6 +3870,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128838001</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3850,6 +3995,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128838036</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3970,6 +4120,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128838328</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4082,6 +4237,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128842520</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4190,6 +4350,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128838005</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4298,6 +4463,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128838045</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4405,6 +4575,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128838042</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4512,8 +4687,50 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128838043</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>